--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="94">
   <si>
     <t xml:space="preserve">Lista de componentes, Control de Inserción de Trama</t>
   </si>
@@ -112,6 +112,15 @@
     <t xml:space="preserve">Pull-ups en IN1/IN2/IN3 (relés) + 2 de sensado Avanzar/Impulso</t>
   </si>
   <si>
+    <t xml:space="preserve">Capacitor electrolítico de 220 a 470 µF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sostienen ante un consumo brusco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando la bobina de un relé engancha tira unos 70 mA de golpe, y si en ese instante el ESP32 está transmitiendo por WiFi (que le pide picos de hasta 300 mA), la fuente no responde lo bastante rápido y la tensión cae lo suficiente para reiniciarlo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protoboard de ensayo y cables</t>
   </si>
   <si>
@@ -142,7 +151,7 @@
     <t xml:space="preserve">Protege la entrada de 220V del HLK-5M05 (su datasheet pide 1A)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cable multifilar 6 conductores, 1 mm² (sin malla)</t>
+    <t xml:space="preserve">Cable multifilar 6 conductores, 1 mm² </t>
   </si>
   <si>
     <t xml:space="preserve">Marcha + Pausa + Retroceder</t>
@@ -175,12 +184,27 @@
     <t xml:space="preserve">Ya se tiene. Punto de montaje a determinar con el telar en marcha: qué eje completa un giro por pasada.</t>
   </si>
   <si>
+    <t xml:space="preserve">Regulador 7824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si la tensión viene alta, la recorta a 24 V clavados. No importa si la entrada son 33 o 36: la salida es 24.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El error que no podés cometer es pasarte de 36, y el regulador lo hace imposible. El otro extremo no tiene consecuencia.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aísla la señal del sensor inductivo (hasta 36V) del GPIO del ESP32</t>
   </si>
   <si>
     <t xml:space="preserve">Uno en uso y uno de repuesto. Mismo componente que el sensado del Bloque A.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cable 3 conectores (para sensor inductivo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conexión entre el gabinete y los el sensor inductivo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resistencia 2,2 kΩ 1 W</t>
   </si>
   <si>
@@ -217,24 +241,18 @@
     <t xml:space="preserve">A fabricar: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
   </si>
   <si>
-    <t xml:space="preserve">(no aplica: el sensor se alimenta desde el telar)</t>
+    <t xml:space="preserve">BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobinas de selección del telar (YA INSTALADAS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El actuador: empuja la palanca de selección. MODELO Y CANTIDAD según la medición (fuerza ≥ el doble de la medida)</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">El dueño de la planta ofreció alimentar el sensor desde la propia máquina, que ya dispone de continua en el rango que el sensor necesita (6 a 36 V). Confirmado el 06/09/26.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bobinas de selección del telar (YA INSTALADAS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El actuador: empuja la palanca de selección. MODELO Y CANTIDAD según la medición (fuerza ≥ el doble de la medida)</t>
-  </si>
-  <si>
     <t xml:space="preserve">El telar cuenta con 6 bobinas en funcionamiento, confirmado con el dueño el 06/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
   </si>
   <si>
@@ -256,16 +274,16 @@
     <t xml:space="preserve">Para el conexionado de los seis canales dentro del gabinete, más repuestos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cable y borneras para los 6 canales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conexión entre el gabinete y los lectores ópticos del telar</t>
+    <t xml:space="preserve">Cable para los 6 canales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conexión entre el gabinete y los rele de estado solido</t>
   </si>
   <si>
     <t xml:space="preserve">Se aprovecha el sobrante del cable del Bloque A. Cantidad a definir según el recorrido real.</t>
   </si>
   <si>
-    <t xml:space="preserve">Polarización de las 3 salidas del ESP32 hacia los SSR</t>
+    <t xml:space="preserve">Polarización de las 6 salidas del ESP32 hacia los SSR</t>
   </si>
   <si>
     <t xml:space="preserve">Una por canal: polarizan las 6 salidas del ESP32 para el arranque seguro.</t>
@@ -290,9 +308,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * \-??_-;_-@"/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* \-??_ ;_-@_ "/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -304,17 +323,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
@@ -661,204 +680,236 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1111,17 +1162,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.4375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Z1003"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="55.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="55.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="50.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="8" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="50.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="8" style="1" width="8.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1336,11 +1387,11 @@
         <v>1</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>3463</v>
+        <v>5000</v>
       </c>
       <c r="E7" s="13" t="n">
         <f aca="false">C7*D7</f>
-        <v>3463</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>15</v>
@@ -1551,11 +1602,11 @@
         <v>3</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">C12*D12</f>
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>19</v>
@@ -1637,17 +1688,17 @@
         <v>1</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>15000</v>
+        <v>300</v>
       </c>
       <c r="E14" s="13" t="n">
         <f aca="false">C14*D14</f>
-        <v>15000</v>
-      </c>
-      <c r="F14" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="24" t="s">
         <v>32</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -1669,28 +1720,28 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>35</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="13" t="n">
         <f aca="false">C15*D15</f>
-        <v>16000</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>19</v>
+        <v>15000</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -1714,20 +1765,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>1200</v>
+        <v>16000</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">C16*D16</f>
-        <v>4800</v>
+        <v>16000</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>19</v>
@@ -1757,20 +1808,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E17" s="13" t="n">
         <f aca="false">C17*D17</f>
-        <v>500</v>
+        <v>3200</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>19</v>
@@ -1798,28 +1849,28 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">C18*D18</f>
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1841,27 +1892,27 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="10" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="19" t="n">
-        <v>400</v>
+      <c r="D19" s="12" t="n">
+        <v>2500</v>
       </c>
       <c r="E19" s="13" t="n">
         <f aca="false">C19*D19</f>
-        <v>1200</v>
+        <v>7500</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="15" t="s">
         <v>45</v>
       </c>
       <c r="H19" s="3"/>
@@ -1884,19 +1935,29 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26" t="s">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27" t="n">
-        <f aca="false">SUM(E6:E19)</f>
-        <v>74116</v>
-      </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
+      <c r="B20" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <f aca="false">C20*D20</f>
+        <v>1200</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>48</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -1917,7 +1978,19 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28" t="n">
+        <f aca="false">SUM(E6:E20)</f>
+        <v>73653</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1938,16 +2011,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1968,28 +2032,16 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>8</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -2010,28 +2062,27 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <f aca="false">C24*D24</f>
-        <v>7000</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>50</v>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -2053,28 +2104,28 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="34" t="s">
         <v>51</v>
       </c>
+      <c r="B25" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="C25" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>700</v>
+        <v>7000</v>
       </c>
       <c r="E25" s="13" t="n">
         <f aca="false">C25*D25</f>
-        <v>1400</v>
-      </c>
-      <c r="F25" s="33" t="s">
+        <v>7000</v>
+      </c>
+      <c r="F25" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="35" t="s">
-        <v>52</v>
+      <c r="G25" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -2096,28 +2147,28 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="10" t="s">
         <v>54</v>
       </c>
+      <c r="B26" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="C26" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">C26*D26</f>
-        <v>300</v>
-      </c>
-      <c r="F26" s="33" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F26" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="35" t="s">
-        <v>55</v>
+      <c r="G26" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -2139,27 +2190,27 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="35" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="E27" s="13" t="n">
         <f aca="false">C27*D27</f>
-        <v>150</v>
-      </c>
-      <c r="F27" s="33" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F27" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="36" t="s">
         <v>58</v>
       </c>
       <c r="H27" s="3"/>
@@ -2182,28 +2233,28 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>23</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E28" s="13" t="n">
         <f aca="false">C28*D28</f>
-        <v>300</v>
-      </c>
-      <c r="F28" s="33" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="35" t="s">
-        <v>61</v>
+      <c r="G28" s="15" t="s">
+        <v>12</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -2225,28 +2276,28 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>60</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="E29" s="13" t="n">
         <f aca="false">C29*D29</f>
-        <v>1000</v>
-      </c>
-      <c r="F29" s="33" t="s">
+        <v>5100</v>
+      </c>
+      <c r="F29" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="36" t="s">
-        <v>64</v>
+      <c r="G29" s="15" t="s">
+        <v>12</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -2268,28 +2319,28 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>66</v>
+        <v>61</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E30" s="13" t="n">
         <f aca="false">C30*D30</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="F30" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="35" t="s">
-        <v>67</v>
+      <c r="G30" s="36" t="s">
+        <v>63</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -2311,19 +2362,29 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37"/>
-      <c r="B31" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="38" t="n">
-        <f aca="false">SUM(E24:E30)</f>
-        <v>10150</v>
-      </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="28"/>
+    <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <f aca="false">C31*D31</f>
+        <v>150</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>66</v>
+      </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -2344,7 +2405,29 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">C32*D32</f>
+        <v>300</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>69</v>
+      </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2365,16 +2448,29 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
+    <row r="33" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <f aca="false">C33*D33</f>
+        <v>1500</v>
+      </c>
+      <c r="F33" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>72</v>
+      </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -2395,28 +2491,19 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="32" t="s">
-        <v>8</v>
-      </c>
+    <row r="34" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="38"/>
+      <c r="B34" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="39" t="n">
+        <f aca="false">SUM(E25:E33)</f>
+        <v>18750</v>
+      </c>
+      <c r="F34" s="40"/>
+      <c r="G34" s="29"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -2437,29 +2524,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="13" t="n">
-        <f aca="false">C35*D35</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>71</v>
-      </c>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -2480,29 +2545,16 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="10" t="s">
+    <row r="36" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <f aca="false">C36*D36</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="36" t="s">
-        <v>74</v>
-      </c>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -2523,28 +2575,27 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="11" t="n">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="43" t="s">
         <v>8</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>600</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <f aca="false">C37*D37</f>
-        <v>4800</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="41" t="s">
-        <v>77</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -2566,28 +2617,28 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="13" t="n">
         <f aca="false">C38*D38</f>
         <v>0</v>
       </c>
-      <c r="F38" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" s="41" t="s">
-        <v>80</v>
+      <c r="F38" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>77</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2609,28 +2660,28 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C39" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>150</v>
+        <v>3700</v>
       </c>
       <c r="E39" s="13" t="n">
         <f aca="false">C39*D39</f>
-        <v>900</v>
-      </c>
-      <c r="F39" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>82</v>
+        <v>22200</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>80</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2652,28 +2703,28 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="45" t="n">
+        <v>600</v>
+      </c>
+      <c r="E40" s="46" t="n">
+        <f aca="false">C40*D40</f>
+        <v>4800</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="36" t="s">
         <v>83</v>
-      </c>
-      <c r="B40" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" s="19" t="n">
-        <v>150</v>
-      </c>
-      <c r="E40" s="43" t="n">
-        <f aca="false">C40*D40</f>
-        <v>900</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="G40" s="41" t="s">
-        <v>85</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -2695,19 +2746,29 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="37"/>
-      <c r="B41" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="38" t="n">
-        <f aca="false">SUM(E35:E40)</f>
-        <v>6600</v>
-      </c>
-      <c r="F41" s="39"/>
-      <c r="G41" s="28"/>
+    <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <f aca="false">C41*D41</f>
+        <v>7700</v>
+      </c>
+      <c r="F41" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" s="36" t="s">
+        <v>86</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -2728,7 +2789,29 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <f aca="false">C42*D42</f>
+        <v>900</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
@@ -2749,19 +2832,29 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="44"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>150</v>
+      </c>
       <c r="E43" s="46" t="n">
-        <f aca="false">E20+E31+E41</f>
-        <v>90866</v>
-      </c>
-      <c r="F43" s="47"/>
-      <c r="G43" s="48"/>
+        <f aca="false">C43*D43</f>
+        <v>900</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>91</v>
+      </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -2782,7 +2875,19 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="47"/>
+      <c r="B44" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="49" t="n">
+        <f aca="false">SUM(E38:E43)</f>
+        <v>36500</v>
+      </c>
+      <c r="F44" s="50"/>
+      <c r="G44" s="51"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -2803,11 +2908,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="49"/>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -2828,9 +2929,19 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49"/>
-      <c r="B46" s="49"/>
+    <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="54" t="n">
+        <f aca="false">E21+E34+E44</f>
+        <v>128903</v>
+      </c>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -2851,9 +2962,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49"/>
-      <c r="B47" s="49"/>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -2874,9 +2983,11 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="49"/>
-      <c r="B48" s="49"/>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="57"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
@@ -2897,13 +3008,9 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -2925,6 +3032,8 @@
       <c r="Z49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -2946,12 +3055,8 @@
       <c r="Z50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
@@ -2973,6 +3078,12 @@
       <c r="Z51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
@@ -2993,14 +3104,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
@@ -3021,12 +3125,11 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -3049,7 +3152,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
@@ -3071,6 +3174,13 @@
       <c r="Z55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
@@ -3092,6 +3202,13 @@
       <c r="Z56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
@@ -7060,9 +7177,69 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
     </row>
-    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H246" s="3"/>
+      <c r="I246" s="3"/>
+      <c r="J246" s="3"/>
+      <c r="K246" s="3"/>
+      <c r="L246" s="3"/>
+      <c r="M246" s="3"/>
+      <c r="N246" s="3"/>
+      <c r="O246" s="3"/>
+      <c r="P246" s="3"/>
+      <c r="Q246" s="3"/>
+      <c r="R246" s="3"/>
+      <c r="S246" s="3"/>
+      <c r="T246" s="3"/>
+      <c r="U246" s="3"/>
+      <c r="V246" s="3"/>
+      <c r="W246" s="3"/>
+      <c r="X246" s="3"/>
+      <c r="Y246" s="3"/>
+      <c r="Z246" s="3"/>
+    </row>
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H247" s="3"/>
+      <c r="I247" s="3"/>
+      <c r="J247" s="3"/>
+      <c r="K247" s="3"/>
+      <c r="L247" s="3"/>
+      <c r="M247" s="3"/>
+      <c r="N247" s="3"/>
+      <c r="O247" s="3"/>
+      <c r="P247" s="3"/>
+      <c r="Q247" s="3"/>
+      <c r="R247" s="3"/>
+      <c r="S247" s="3"/>
+      <c r="T247" s="3"/>
+      <c r="U247" s="3"/>
+      <c r="V247" s="3"/>
+      <c r="W247" s="3"/>
+      <c r="X247" s="3"/>
+      <c r="Y247" s="3"/>
+      <c r="Z247" s="3"/>
+    </row>
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H248" s="3"/>
+      <c r="I248" s="3"/>
+      <c r="J248" s="3"/>
+      <c r="K248" s="3"/>
+      <c r="L248" s="3"/>
+      <c r="M248" s="3"/>
+      <c r="N248" s="3"/>
+      <c r="O248" s="3"/>
+      <c r="P248" s="3"/>
+      <c r="Q248" s="3"/>
+      <c r="R248" s="3"/>
+      <c r="S248" s="3"/>
+      <c r="T248" s="3"/>
+      <c r="U248" s="3"/>
+      <c r="V248" s="3"/>
+      <c r="W248" s="3"/>
+      <c r="X248" s="3"/>
+      <c r="Y248" s="3"/>
+      <c r="Z248" s="3"/>
+    </row>
     <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7815,33 +7992,36 @@
     <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1002" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1003" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="H1:Z3"/>
     <mergeCell ref="A2:G3"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:Z245"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A45:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="H4:Z248"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A48:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A57:G57"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" display="https://candy-ho.com/producto/nodemcu-esp32-wifi-bluetooth-4-2-iot-wroom-esp32s-arduino/"/>
     <hyperlink ref="F7" r:id="rId2" display="https://candy-ho.com/producto/modulo-relay-rele-de-2-canales-5v-10a-arduino-pic-avr-2/"/>
-    <hyperlink ref="F14" r:id="rId3" display="https://candy-ho.com/producto/tiras-de-40-pines-hembra-paso-2-54mm-recta-1-fila-arduino/   -  https://candy-ho.com/producto/pcb-placa-experimental-doble-7x9-prototipos-electronica-fr4/"/>
+    <hyperlink ref="F15" r:id="rId3" display="https://candy-ho.com/producto/tiras-de-40-pines-hembra-paso-2-54mm-recta-1-fila-arduino/   -  https://candy-ho.com/producto/pcb-placa-experimental-doble-7x9-prototipos-electronica-fr4/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -323,17 +323,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="96">
   <si>
     <t xml:space="preserve">Lista de componentes, Control de Inserción de Trama</t>
   </si>
@@ -184,10 +184,10 @@
     <t xml:space="preserve">Ya se tiene. Punto de montaje a determinar con el telar en marcha: qué eje completa un giro por pasada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulador 7824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si la tensión viene alta, la recorta a 24 V clavados. No importa si la entrada son 33 o 36: la salida es 24.</t>
+    <t xml:space="preserve">(no aplica) Regulador 7824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya no es necesario: el telar entrega 12 a 14 V continuos, muy por debajo de los 36 V que tolera el sensor</t>
   </si>
   <si>
     <t xml:space="preserve">El error que no podés cometer es pasarte de 36, y el regulador lo hace imposible. El otro extremo no tiene consecuencia.</t>
@@ -199,16 +199,22 @@
     <t xml:space="preserve">Uno en uso y uno de repuesto. Mismo componente que el sensado del Bloque A.</t>
   </si>
   <si>
+    <t xml:space="preserve">(no aplica) Puente rectificador DB157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya no es necesario para este bloque: la alimentación del sensor ya viene en continua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cable 3 conectores (para sensor inductivo)</t>
   </si>
   <si>
     <t xml:space="preserve">Conexión entre el gabinete y los el sensor inductivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Resistencia 2,2 kΩ 1 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limita la corriente del LED del optoacoplador</t>
+    <t xml:space="preserve">Resistencia 1,2 kΩ ¼ W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limita la corriente del LED del optoacoplador. Con 13 V da unos 10 mA, el valor de trabajo del PC817</t>
   </si>
   <si>
     <t xml:space="preserve">Uno en uso y uno de repuesto.</t>
@@ -223,19 +229,19 @@
     <t xml:space="preserve">Mantiene el pin del ESP32 en nivel alto mientras el sensor no detecta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Capacitor cerámico 100nF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtrado fino en el colector del opto</t>
+    <t xml:space="preserve">(no aplica) Capacitor cerámico 100 nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompañaba al regulador, que ya no se usa</t>
   </si>
   <si>
     <t xml:space="preserve">Filtra el ruido del elevador de tensión.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blanco metálico + soporte/escuadra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tornillo o chapita al eje + montaje del sensor</t>
+    <t xml:space="preserve">Blanco metálico y soporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paleta de acero sobre el eje y escuadra de montaje. Soporte ya construido</t>
   </si>
   <si>
     <t xml:space="preserve">A fabricar: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
@@ -323,17 +329,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="IBM Plex Sans"/>
+      <name val="Arial"/>
       <family val="0"/>
     </font>
     <font>
@@ -685,7 +691,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -693,11 +699,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -745,11 +751,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -757,11 +763,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -781,11 +787,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -793,11 +799,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -833,15 +839,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -893,7 +899,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -901,11 +907,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2155,14 +2161,14 @@
         <v>55</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">C26*D26</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F26" s="34" t="s">
         <v>19</v>
@@ -2235,20 +2241,20 @@
     </row>
     <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" s="12" t="n">
         <v>500</v>
       </c>
       <c r="E28" s="13" t="n">
         <f aca="false">C28*D28</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F28" s="34" t="s">
         <v>19</v>
@@ -2278,10 +2284,10 @@
     </row>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C29" s="11" t="n">
         <v>3</v>
@@ -2321,10 +2327,10 @@
     </row>
     <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C30" s="11" t="n">
         <v>2</v>
@@ -2340,7 +2346,7 @@
         <v>19</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -2364,10 +2370,10 @@
     </row>
     <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31" s="11" t="n">
         <v>1</v>
@@ -2383,7 +2389,7 @@
         <v>19</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -2407,26 +2413,26 @@
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="12" t="n">
         <v>300</v>
       </c>
       <c r="E32" s="13" t="n">
         <f aca="false">C32*D32</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F32" s="34" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -2450,26 +2456,26 @@
     </row>
     <row r="33" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="E33" s="13" t="n">
         <f aca="false">C33*D33</f>
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F33" s="34" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2500,7 +2506,7 @@
       <c r="D34" s="27"/>
       <c r="E34" s="39" t="n">
         <f aca="false">SUM(E25:E33)</f>
-        <v>18750</v>
+        <v>13950</v>
       </c>
       <c r="F34" s="40"/>
       <c r="G34" s="29"/>
@@ -2547,7 +2553,7 @@
     </row>
     <row r="36" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -2619,10 +2625,10 @@
     </row>
     <row r="38" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="11" t="n">
         <v>6</v>
@@ -2635,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2662,10 +2668,10 @@
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C39" s="11" t="n">
         <v>6</v>
@@ -2678,10 +2684,10 @@
         <v>22200</v>
       </c>
       <c r="F39" s="34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2705,10 +2711,10 @@
     </row>
     <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C40" s="11" t="n">
         <v>8</v>
@@ -2724,7 +2730,7 @@
         <v>19</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -2748,10 +2754,10 @@
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C41" s="11" t="n">
         <v>11</v>
@@ -2764,10 +2770,10 @@
         <v>7700</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G41" s="36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -2791,10 +2797,10 @@
     </row>
     <row r="42" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C42" s="11" t="n">
         <v>6</v>
@@ -2810,7 +2816,7 @@
         <v>19</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -2834,10 +2840,10 @@
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C43" s="11" t="n">
         <v>6</v>
@@ -2853,7 +2859,7 @@
         <v>19</v>
       </c>
       <c r="G43" s="36" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -2931,14 +2937,14 @@
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="52" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B46" s="52"/>
       <c r="C46" s="53"/>
       <c r="D46" s="53"/>
       <c r="E46" s="54" t="n">
         <f aca="false">E21+E34+E44</f>
-        <v>128903</v>
+        <v>124103</v>
       </c>
       <c r="F46" s="55"/>
       <c r="G46" s="56"/>
@@ -2985,7 +2991,7 @@
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="57" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B48" s="57"/>
       <c r="H48" s="3"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -247,19 +247,19 @@
     <t xml:space="preserve">A fabricar: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
   </si>
   <si>
-    <t xml:space="preserve">BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN </t>
+    <t xml:space="preserve">BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN (4 canales en el C 401)</t>
   </si>
   <si>
     <t xml:space="preserve">Bobinas de selección del telar (YA INSTALADAS)</t>
   </si>
   <si>
-    <t xml:space="preserve">El actuador: empuja la palanca de selección. MODELO Y CANTIDAD según la medición (fuerza ≥ el doble de la medida)</t>
+    <t xml:space="preserve">El actuador: empuja la palanca de selección. El C 401 elegido tiene cuatro</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">El telar cuenta con 6 bobinas en funcionamiento, confirmado con el dueño el 06/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
+    <t xml:space="preserve">El C 401 elegido tiene 4 bobinas en funcionamiento, confirmado con el dueño el 06/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
   </si>
   <si>
     <t xml:space="preserve">Relé PhotoMOS Panasonic AQY212GH (DIP-4)</t>
@@ -277,10 +277,10 @@
     <t xml:space="preserve">Empalme al cableado del telar sin soldar sobre los cables viejos</t>
   </si>
   <si>
-    <t xml:space="preserve">Para el conexionado de los seis canales dentro del gabinete, más repuestos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cable para los 6 canales</t>
+    <t xml:space="preserve">Para el conexionado de los cuatro canales dentro del gabinete, más repuestos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable para los 4 canales</t>
   </si>
   <si>
     <t xml:space="preserve">Conexión entre el gabinete y los rele de estado solido</t>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">Se aprovecha el sobrante del cable del Bloque A. Cantidad a definir según el recorrido real.</t>
   </si>
   <si>
-    <t xml:space="preserve">Polarización de las 6 salidas del ESP32 hacia los SSR</t>
+    <t xml:space="preserve">Polarización de las 4 salidas del ESP32 hacia los relés</t>
   </si>
   <si>
     <t xml:space="preserve">Una por canal: polarizan las 6 salidas del ESP32 para el arranque seguro.</t>
@@ -329,17 +329,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="IBM Plex Sans"/>
       <family val="0"/>
     </font>
     <font>
@@ -2631,7 +2631,7 @@
         <v>77</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" s="12" t="n">
         <v>0</v>
@@ -2674,14 +2674,14 @@
         <v>81</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" s="12" t="n">
         <v>3700</v>
       </c>
       <c r="E39" s="13" t="n">
         <f aca="false">C39*D39</f>
-        <v>22200</v>
+        <v>14800</v>
       </c>
       <c r="F39" s="34" t="s">
         <v>78</v>
@@ -2717,14 +2717,14 @@
         <v>84</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" s="45" t="n">
         <v>600</v>
       </c>
       <c r="E40" s="46" t="n">
         <f aca="false">C40*D40</f>
-        <v>4800</v>
+        <v>3600</v>
       </c>
       <c r="F40" s="34" t="s">
         <v>19</v>
@@ -2760,14 +2760,14 @@
         <v>87</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>700</v>
       </c>
       <c r="E41" s="13" t="n">
         <f aca="false">C41*D41</f>
-        <v>7700</v>
+        <v>5600</v>
       </c>
       <c r="F41" s="34" t="s">
         <v>78</v>
@@ -2803,14 +2803,14 @@
         <v>89</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" s="12" t="n">
         <v>150</v>
       </c>
       <c r="E42" s="13" t="n">
         <f aca="false">C42*D42</f>
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F42" s="34" t="s">
         <v>19</v>
@@ -2846,14 +2846,14 @@
         <v>92</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>150</v>
       </c>
       <c r="E43" s="46" t="n">
         <f aca="false">C43*D43</f>
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F43" s="34" t="s">
         <v>19</v>
@@ -2890,7 +2890,7 @@
       <c r="D44" s="48"/>
       <c r="E44" s="49" t="n">
         <f aca="false">SUM(E38:E43)</f>
-        <v>36500</v>
+        <v>25200</v>
       </c>
       <c r="F44" s="50"/>
       <c r="G44" s="51"/>
@@ -2944,7 +2944,7 @@
       <c r="D46" s="53"/>
       <c r="E46" s="54" t="n">
         <f aca="false">E21+E34+E44</f>
-        <v>124103</v>
+        <v>112803</v>
       </c>
       <c r="F46" s="55"/>
       <c r="G46" s="56"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Resistencias 10kΩ ¼W</t>
   </si>
   <si>
-    <t xml:space="preserve">Pull-ups en IN1/IN2/IN3 (relés) + 2 de sensado Avanzar/Impulso</t>
+    <t xml:space="preserve">Relés: pull-up en IN1 e IN2, pull-down a GND en IN3 (con pull-up el relé de Retroceder arranca cerrado). Sensado: pull-up en GPIO 32, 33 y 34 (Marcha, Pausa, Retroceder)</t>
   </si>
   <si>
     <t xml:space="preserve">Capacitor electrolítico de 220 a 470 µF</t>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">Corta la señal de cada lector óptico, comandado directo desde un pin del ESP32</t>
   </si>
   <si>
-    <t xml:space="preserve">Uno por lector óptico: son 6, uno por bobina de selección, confirmado con el dueño el 06/09/26. Se elige PhotoMOS y NO un SSR de triac: el triac necesita 0,1 A de corriente mínima para mantenerse encendido y la señal del lector probablemente maneje pocos miliamperes, con lo que un SSR no encendería. Además el SSR deja pasar hasta 2 mA apagado, que la plaqueta podría leer como señal presente. IMPORTANTE: la letra final del código define el encapsulado. H = DIP de inserción (el que sirve para la placa perforada), S = montaje superficial. Alternativa: AQY212EH. Comprar 1 y probar antes de los 6.</t>
+    <t xml:space="preserve">Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 06/09/26. Se elige PhotoMOS y NO un SSR de triac: el triac necesita 0,1 A de corriente mínima para mantenerse encendido y la señal del lector probablemente maneje pocos miliamperes, con lo que un SSR no encendería. Además el SSR deja pasar hasta 2 mA apagado, que la plaqueta podría leer como señal presente. IMPORTANTE: la letra final del código define el encapsulado. H = DIP de inserción (el que sirve para la placa perforada), S = montaje superficial. Alternativa: AQY212EH. Comprar 1 y probar antes de los 6.</t>
   </si>
   <si>
     <t xml:space="preserve">Borneras atornillables chicas</t>
@@ -292,7 +292,7 @@
     <t xml:space="preserve">Polarización de las 4 salidas del ESP32 hacia los relés</t>
   </si>
   <si>
-    <t xml:space="preserve">Una por canal: polarizan las 6 salidas del ESP32 para el arranque seguro.</t>
+    <t xml:space="preserve">Una por canal: polarizan las 4 salidas del ESP32 para el arranque seguro.</t>
   </si>
   <si>
     <t xml:space="preserve">Resistencia 330 Ω ¼ W</t>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -97,7 +97,7 @@
     <t xml:space="preserve">Resistencia 2,2kΩ 1W</t>
   </si>
   <si>
-    <t xml:space="preserve">Limita la corriente hacia el LED del PC817</t>
+    <t xml:space="preserve">Limita la corriente hacia el LED del PC817. Es el valor para una botonera de 18 a 24 V: si al medirla diera entre 12 y 18 V, va de 1,2 kΩ. Es el valor para una botonera de 18 a 24 V: si al medirla diera entre 12 y 18 V, va de 1,2 kΩ</t>
   </si>
   <si>
     <t xml:space="preserve">Capacitores cerámicos 100nF</t>
@@ -262,13 +262,13 @@
     <t xml:space="preserve">El C 401 elegido tiene 4 bobinas en funcionamiento, confirmado con el dueño el 06/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
   </si>
   <si>
-    <t xml:space="preserve">Relé PhotoMOS Panasonic AQY212GH (DIP-4)</t>
+    <t xml:space="preserve">Relé OptoMOS LCA110 de IXYS (DIP-6)</t>
   </si>
   <si>
     <t xml:space="preserve">Corta la señal de cada lector óptico, comandado directo desde un pin del ESP32</t>
   </si>
   <si>
-    <t xml:space="preserve">Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 06/09/26. Se elige PhotoMOS y NO un SSR de triac: el triac necesita 0,1 A de corriente mínima para mantenerse encendido y la señal del lector probablemente maneje pocos miliamperes, con lo que un SSR no encendería. Además el SSR deja pasar hasta 2 mA apagado, que la plaqueta podría leer como señal presente. IMPORTANTE: la letra final del código define el encapsulado. H = DIP de inserción (el que sirve para la placa perforada), S = montaje superficial. Alternativa: AQY212EH. Comprar 1 y probar antes de los 6.</t>
+    <t xml:space="preserve">Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 06/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1, TLP3021 (cada uno con su propia disposición de patas). Comprar 1 y probarlo antes de los otros 3.</t>
   </si>
   <si>
     <t xml:space="preserve">Borneras atornillables chicas</t>
@@ -298,7 +298,7 @@
     <t xml:space="preserve">Resistencia 330 Ω ¼ W</t>
   </si>
   <si>
-    <t xml:space="preserve">Limita la corriente del LED de entrada de cada relé PhotoMOS</t>
+    <t xml:space="preserve">Limita la corriente del LED de entrada de cada relé LCA110</t>
   </si>
   <si>
     <t xml:space="preserve">Una por canal. Con los 3,3 V del ESP32 entrega unos 6 mA. NO es opcional: sin ella se daña el LED del relé. El SSR de triac no la necesita porque la trae incorporada.</t>
@@ -2677,11 +2677,11 @@
         <v>4</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>3700</v>
+        <v>6034</v>
       </c>
       <c r="E39" s="13" t="n">
         <f aca="false">C39*D39</f>
-        <v>14800</v>
+        <v>24136</v>
       </c>
       <c r="F39" s="34" t="s">
         <v>78</v>
@@ -2890,7 +2890,7 @@
       <c r="D44" s="48"/>
       <c r="E44" s="49" t="n">
         <f aca="false">SUM(E38:E43)</f>
-        <v>25200</v>
+        <v>34536</v>
       </c>
       <c r="F44" s="50"/>
       <c r="G44" s="51"/>
@@ -2944,7 +2944,7 @@
       <c r="D46" s="53"/>
       <c r="E46" s="54" t="n">
         <f aca="false">E21+E34+E44</f>
-        <v>112803</v>
+        <v>122139</v>
       </c>
       <c r="F46" s="55"/>
       <c r="G46" s="56"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -181,7 +181,7 @@
     <t xml:space="preserve">Sensor de pasada recomendado, inmune a la pelusa. Incluye 1 repuesto, esto es lo que le da al ESP32 el "entendimiento" de movimiento y posición del telar</t>
   </si>
   <si>
-    <t xml:space="preserve">Ya se tiene. Punto de montaje a determinar con el telar en marcha: qué eje completa un giro por pasada.</t>
+    <t xml:space="preserve">Ya se tiene. Montado el 10/09/2026 sobre un eje que da una vuelta por pasada.</t>
   </si>
   <si>
     <t xml:space="preserve">(no aplica) Regulador 7824</t>
@@ -247,19 +247,19 @@
     <t xml:space="preserve">A fabricar: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
   </si>
   <si>
-    <t xml:space="preserve">BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN (4 canales en el C 401)</t>
+    <t xml:space="preserve">BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN (4 canales en el C 201)</t>
   </si>
   <si>
     <t xml:space="preserve">Bobinas de selección del telar (YA INSTALADAS)</t>
   </si>
   <si>
-    <t xml:space="preserve">El actuador: empuja la palanca de selección. El C 401 elegido tiene cuatro</t>
+    <t xml:space="preserve">El actuador: empuja la palanca de selección. El C 201 tiene cuatro</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">El C 401 elegido tiene 4 bobinas en funcionamiento, confirmado con el dueño el 06/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
+    <t xml:space="preserve">El C 201 tiene 4 bobinas en funcionamiento, confirmado con el dueño el 19/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
   </si>
   <si>
     <t xml:space="preserve">Relé OptoMOS LCA110 de IXYS (DIP-6)</t>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B7" s="69" t="inlineStr">
         <is>
-          <t>En paralelo a los botones Marcha/Pausa del telar</t>
+          <t>En paralelo a los botones Marcha, Pausa y Retroceder del telar</t>
         </is>
       </c>
       <c r="C7" s="70" t="n">

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1120,7 +1120,7 @@
     <row r="4" ht="19.5" customHeight="1" s="59">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>BLOQUE A, Nivel 1: Marcha/Pausa en el telar  (Etapa 4)</t>
+          <t>BLOQUE A, Nivel 1: Marcha, Pausa y Retroceder en el telar  (Etapa 4)</t>
         </is>
       </c>
       <c r="B4" s="63" t="n"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -2262,72 +2262,217 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1" s="59">
-      <c r="A44" s="111" t="n"/>
-      <c r="B44" s="112" t="inlineStr">
+    <row r="44" ht="33.75" customHeight="1" s="59">
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>Placa experimental (plaqueta) adicional</t>
+        </is>
+      </c>
+      <c r="B44" s="69" t="inlineStr">
+        <is>
+          <t>Pasar a placa soldada el circuito del Nivel 2 que ya funcionó en protoboard</t>
+        </is>
+      </c>
+      <c r="C44" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="71" t="n"/>
+      <c r="E44" s="72">
+        <f>C44*D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026: con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="33.75" customHeight="1" s="59">
+      <c r="A45" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 2 (2x)</t>
+        </is>
+      </c>
+      <c r="B45" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C45" s="70" t="n">
+        <v>19</v>
+      </c>
+      <c r="D45" s="71" t="n"/>
+      <c r="E45" s="72">
+        <f>C45*D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Permiten sacar módulos y cables sin desoldar. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="33.75" customHeight="1" s="59">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 5 (5x)</t>
+        </is>
+      </c>
+      <c r="B46" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C46" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="71" t="n"/>
+      <c r="E46" s="72">
+        <f>C46*D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="33.75" customHeight="1" s="59">
+      <c r="A47" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 6 (6x)</t>
+        </is>
+      </c>
+      <c r="B47" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C47" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="71" t="n"/>
+      <c r="E47" s="72">
+        <f>C47*D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="33.75" customHeight="1" s="59">
+      <c r="A48" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 8 (8x)</t>
+        </is>
+      </c>
+      <c r="B48" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C48" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="71" t="n"/>
+      <c r="E48" s="72">
+        <f>C48*D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" s="59">
+      <c r="A49" s="111" t="n"/>
+      <c r="B49" s="112" t="inlineStr">
         <is>
           <t>Subtotal bloque</t>
         </is>
       </c>
-      <c r="C44" s="87" t="n"/>
-      <c r="D44" s="88" t="n"/>
-      <c r="E44" s="113">
-        <f>SUM(E38:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="114" t="n"/>
-      <c r="G44" s="115" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1" s="59"/>
-    <row r="46" ht="24" customHeight="1" s="59">
-      <c r="A46" s="116" t="inlineStr">
+      <c r="C49" s="87" t="n"/>
+      <c r="D49" s="88" t="n"/>
+      <c r="E49" s="113">
+        <f>SUM(E38:E48)</f>
+        <v/>
+      </c>
+      <c r="F49" s="114" t="n"/>
+      <c r="G49" s="115" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="59"/>
+    <row r="51" ht="24" customHeight="1" s="59">
+      <c r="A51" s="116" t="inlineStr">
         <is>
           <t>TOTAL DEL PROYECTO COMPLETO (A + C + D)</t>
         </is>
       </c>
-      <c r="B46" s="117" t="n"/>
-      <c r="C46" s="118" t="n"/>
-      <c r="D46" s="118" t="n"/>
-      <c r="E46" s="119">
-        <f>E21+E34+E44</f>
-        <v/>
-      </c>
-      <c r="F46" s="120" t="n"/>
-      <c r="G46" s="121" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="59"/>
-    <row r="48" ht="21.75" customHeight="1" s="59">
-      <c r="A48" s="122" t="inlineStr">
-        <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la salida de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, cuya conexión (serie o paralelo) depende de esa medición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="59"/>
-    <row r="50" ht="15" customHeight="1" s="59"/>
-    <row r="51" ht="15" customHeight="1" s="59"/>
-    <row r="52" ht="15" customHeight="1" s="59">
-      <c r="A52" s="58" t="n"/>
-      <c r="C52" s="58" t="n"/>
-      <c r="F52" s="58" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="59"/>
-    <row r="54" ht="15" customHeight="1" s="59">
-      <c r="A54" s="58" t="n"/>
-      <c r="F54" s="58" t="n"/>
-    </row>
+      <c r="B51" s="117" t="n"/>
+      <c r="C51" s="118" t="n"/>
+      <c r="D51" s="118" t="n"/>
+      <c r="E51" s="119">
+        <f>E21+E34+E49</f>
+        <v/>
+      </c>
+      <c r="F51" s="120" t="n"/>
+      <c r="G51" s="121" t="n"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" s="59"/>
+    <row r="53" ht="21.75" customHeight="1" s="59">
+      <c r="A53" s="122" t="inlineStr">
+        <is>
+          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la salida de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, cuya conexión (en serie, en paralelo o en lugar del lector) depende de esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="59"/>
     <row r="55" ht="15" customHeight="1" s="59"/>
-    <row r="56" ht="15.75" customHeight="1" s="59">
-      <c r="A56" s="58" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="59">
+    <row r="56" ht="15" customHeight="1" s="59"/>
+    <row r="57" ht="15" customHeight="1" s="59">
       <c r="A57" s="58" t="n"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" s="59"/>
-    <row r="59" ht="15.75" customHeight="1" s="59"/>
-    <row r="60" ht="15.75" customHeight="1" s="59"/>
-    <row r="61" ht="15.75" customHeight="1" s="59"/>
-    <row r="62" ht="15.75" customHeight="1" s="59"/>
+      <c r="C57" s="58" t="n"/>
+      <c r="F57" s="58" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="59"/>
+    <row r="59" ht="15" customHeight="1" s="59">
+      <c r="A59" s="58" t="n"/>
+      <c r="F59" s="58" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="59"/>
+    <row r="61" ht="15.75" customHeight="1" s="59">
+      <c r="A61" s="58" t="n"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="59">
+      <c r="A62" s="58" t="n"/>
+    </row>
     <row r="63" ht="15.75" customHeight="1" s="59"/>
     <row r="64" ht="15.75" customHeight="1" s="59"/>
     <row r="65" ht="15.75" customHeight="1" s="59"/>
@@ -3271,25 +3416,25 @@
     <row r="1003" ht="15.75" customHeight="1" s="59"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A62:G62"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="A53:B56"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A2:G3"/>
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="H4:Z248"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="A48:B51"/>
     <mergeCell ref="H1:Z3"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="C57:D57"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="F57:G57"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <hyperlinks>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z248"/>
+  <dimension ref="A1:Z252"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55.33" customWidth="1" style="58" min="1" max="1"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B39" s="69" t="inlineStr">
         <is>
-          <t>Corta la señal de cada lector óptico, comandado directo desde un pin del ESP32</t>
+          <t>Da la señal en lugar de cada lector óptico (conexión final), comandado directo desde un pin del ESP32</t>
         </is>
       </c>
       <c r="C39" s="70" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G39" s="101" t="inlineStr">
         <is>
-          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1, TLP3021 (cada uno con su propia disposición de patas). Comprar 1 y probarlo antes de los otros 3.</t>
+          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1, TLP3021 (cada uno con su propia disposición de patas). Conexión final: el relé en lugar del lector, con una resistencia de protección (diagramas/hardware/conexion_final_rele.png). Comprar 1 y probarlo antes de los otros 3.</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G40" s="100" t="inlineStr">
         <is>
-          <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos.</t>
+          <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos. Las del conector de cada lector son las de 4 vías (abajo).</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B41" s="80" t="inlineStr">
         <is>
-          <t>Conexión entre el gabinete y los rele de estado solido</t>
+          <t>Conexión entre el gabinete y el conector de cada lector</t>
         </is>
       </c>
       <c r="C41" s="70" t="n">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="33.75" customHeight="1" s="59">
+    <row r="44" ht="45" customHeight="1" s="59">
       <c r="A44" s="68" t="inlineStr">
         <is>
           <t>Placa experimental (plaqueta) adicional</t>
@@ -2412,71 +2412,187 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1" s="59">
-      <c r="A49" s="111" t="n"/>
-      <c r="B49" s="112" t="inlineStr">
+    <row r="49" ht="45" customHeight="1" s="59">
+      <c r="A49" s="68" t="inlineStr">
+        <is>
+          <t>Zócalo DIP de 6 patas</t>
+        </is>
+      </c>
+      <c r="B49" s="69" t="inlineStr">
+        <is>
+          <t>Permite cambiar un relé LCA110 sin desoldar</t>
+        </is>
+      </c>
+      <c r="C49" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="71" t="n"/>
+      <c r="E49" s="72">
+        <f>C49*D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026: el relé va enchufado en el zócalo, con la muesca del lado de la pata 1. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1" s="59">
+      <c r="A50" s="68" t="inlineStr">
+        <is>
+          <t>Resistencia de protección (220 Ω 2 W o 470 Ω 3 W)</t>
+        </is>
+      </c>
+      <c r="B50" s="69" t="inlineStr">
+        <is>
+          <t>Lado del telar: limita la corriente si hay un error de cableado. Va del + del conector del lector a la pata 4 del relé</t>
+        </is>
+      </c>
+      <c r="C50" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="71" t="n"/>
+      <c r="E50" s="72">
+        <f>C50*D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final (la más segura). 220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V: se elige con la medición. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1" s="59">
+      <c r="A51" s="68" t="inlineStr">
+        <is>
+          <t>Resistencia 10 kΩ ½ W</t>
+        </is>
+      </c>
+      <c r="B51" s="69" t="inlineStr">
+        <is>
+          <t>Lado del telar: de la señal al − de cada conector de lector. Con el relé abierto deja la señal en 0 V, como con papel</t>
+        </is>
+      </c>
+      <c r="C51" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="71" t="n"/>
+      <c r="E51" s="72">
+        <f>C51*D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final. Una por canal. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" s="59">
+      <c r="A52" s="68" t="inlineStr">
+        <is>
+          <t>Borneras de 4 vías</t>
+        </is>
+      </c>
+      <c r="B52" s="69" t="inlineStr">
+        <is>
+          <t>Conector de cada lector en la plaqueta del telar, y para dejar aislados los cables del lector</t>
+        </is>
+      </c>
+      <c r="C52" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="72">
+        <f>C52*D52</f>
+        <v/>
+      </c>
+      <c r="F52" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final. Por canal: una para el conector del lector y otra para dejar aislados y rotulados sus 4 cables, que se vuelven a conectar en minutos. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" s="59">
+      <c r="A53" s="111" t="n"/>
+      <c r="B53" s="112" t="inlineStr">
         <is>
           <t>Subtotal bloque</t>
         </is>
       </c>
-      <c r="C49" s="87" t="n"/>
-      <c r="D49" s="88" t="n"/>
-      <c r="E49" s="113">
-        <f>SUM(E38:E48)</f>
-        <v/>
-      </c>
-      <c r="F49" s="114" t="n"/>
-      <c r="G49" s="115" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="59"/>
-    <row r="51" ht="24" customHeight="1" s="59">
-      <c r="A51" s="116" t="inlineStr">
+      <c r="C53" s="87" t="n"/>
+      <c r="D53" s="88" t="n"/>
+      <c r="E53" s="113">
+        <f>SUM(E38:E52)</f>
+        <v/>
+      </c>
+      <c r="F53" s="114" t="n"/>
+      <c r="G53" s="115" t="n"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="59"/>
+    <row r="55" ht="24" customHeight="1" s="59">
+      <c r="A55" s="116" t="inlineStr">
         <is>
           <t>TOTAL DEL PROYECTO COMPLETO (A + C + D)</t>
         </is>
       </c>
-      <c r="B51" s="117" t="n"/>
-      <c r="C51" s="118" t="n"/>
-      <c r="D51" s="118" t="n"/>
-      <c r="E51" s="119">
-        <f>E21+E34+E49</f>
-        <v/>
-      </c>
-      <c r="F51" s="120" t="n"/>
-      <c r="G51" s="121" t="n"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" s="59"/>
-    <row r="53" ht="21.75" customHeight="1" s="59">
-      <c r="A53" s="122" t="inlineStr">
-        <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la salida de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, cuya conexión (en serie, en paralelo o en lugar del lector) depende de esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" s="59"/>
-    <row r="55" ht="15" customHeight="1" s="59"/>
-    <row r="56" ht="15" customHeight="1" s="59"/>
-    <row r="57" ht="15" customHeight="1" s="59">
-      <c r="A57" s="58" t="n"/>
-      <c r="C57" s="58" t="n"/>
-      <c r="F57" s="58" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="59"/>
-    <row r="59" ht="15" customHeight="1" s="59">
-      <c r="A59" s="58" t="n"/>
-      <c r="F59" s="58" t="n"/>
-    </row>
+      <c r="B55" s="117" t="n"/>
+      <c r="C55" s="118" t="n"/>
+      <c r="D55" s="118" t="n"/>
+      <c r="E55" s="119">
+        <f>E21+E34+E53</f>
+        <v/>
+      </c>
+      <c r="F55" s="120" t="n"/>
+      <c r="G55" s="121" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="59"/>
+    <row r="57" ht="21.75" customHeight="1" s="59">
+      <c r="A57" s="122" t="inlineStr">
+        <is>
+          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la alimentación y la señal de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="59"/>
+    <row r="59" ht="15" customHeight="1" s="59"/>
     <row r="60" ht="15" customHeight="1" s="59"/>
-    <row r="61" ht="15.75" customHeight="1" s="59">
+    <row r="61" ht="15" customHeight="1" s="59">
       <c r="A61" s="58" t="n"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" s="59">
-      <c r="A62" s="58" t="n"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" s="59"/>
-    <row r="64" ht="15.75" customHeight="1" s="59"/>
-    <row r="65" ht="15.75" customHeight="1" s="59"/>
-    <row r="66" ht="15.75" customHeight="1" s="59"/>
+      <c r="C61" s="58" t="n"/>
+      <c r="F61" s="58" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="59"/>
+    <row r="63" ht="15" customHeight="1" s="59">
+      <c r="A63" s="58" t="n"/>
+      <c r="F63" s="58" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="59"/>
+    <row r="65" ht="15.75" customHeight="1" s="59">
+      <c r="A65" s="58" t="n"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="59">
+      <c r="A66" s="58" t="n"/>
+    </row>
     <row r="67" ht="15.75" customHeight="1" s="59"/>
     <row r="68" ht="15.75" customHeight="1" s="59"/>
     <row r="69" ht="15.75" customHeight="1" s="59"/>
@@ -3416,25 +3532,25 @@
     <row r="1003" ht="15.75" customHeight="1" s="59"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="F63:G63"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="A53:B56"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A57:B60"/>
     <mergeCell ref="A2:G3"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="H4:Z248"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="H1:Z3"/>
-    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="H4:Z252"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F57:G57"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <hyperlinks>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z248"/>
+  <dimension ref="A1:Z252"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="55.33" customWidth="1" style="58" min="1" max="1"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B39" s="69" t="inlineStr">
         <is>
-          <t>Corta la señal de cada lector óptico, comandado directo desde un pin del ESP32</t>
+          <t>Da la señal en lugar de cada lector óptico (conexión final), comandado directo desde un pin del ESP32</t>
         </is>
       </c>
       <c r="C39" s="70" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G39" s="101" t="inlineStr">
         <is>
-          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1, TLP3021 (cada uno con su propia disposición de patas). Comprar 1 y probarlo antes de los otros 3.</t>
+          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1, TLP3021 (cada uno con su propia disposición de patas). Conexión final: el relé en lugar del lector, con una resistencia de protección (diagramas/hardware/conexion_final_rele.png). Comprar 1 y probarlo antes de los otros 3.</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G40" s="100" t="inlineStr">
         <is>
-          <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos.</t>
+          <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos. Las del conector de cada lector son las de 4 vías (abajo).</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B41" s="80" t="inlineStr">
         <is>
-          <t>Conexión entre el gabinete y los rele de estado solido</t>
+          <t>Conexión entre el gabinete y el conector de cada lector</t>
         </is>
       </c>
       <c r="C41" s="70" t="n">
@@ -2262,76 +2262,337 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1" s="59">
-      <c r="A44" s="111" t="n"/>
-      <c r="B44" s="112" t="inlineStr">
+    <row r="44" ht="45" customHeight="1" s="59">
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>Placa experimental (plaqueta) adicional</t>
+        </is>
+      </c>
+      <c r="B44" s="69" t="inlineStr">
+        <is>
+          <t>Pasar a placa soldada el circuito del Nivel 2 que ya funcionó en protoboard</t>
+        </is>
+      </c>
+      <c r="C44" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="71" t="n"/>
+      <c r="E44" s="72">
+        <f>C44*D44</f>
+        <v/>
+      </c>
+      <c r="F44" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026: con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="33.75" customHeight="1" s="59">
+      <c r="A45" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 2 (2x)</t>
+        </is>
+      </c>
+      <c r="B45" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C45" s="70" t="n">
+        <v>19</v>
+      </c>
+      <c r="D45" s="71" t="n"/>
+      <c r="E45" s="72">
+        <f>C45*D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Permiten sacar módulos y cables sin desoldar. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="33.75" customHeight="1" s="59">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 5 (5x)</t>
+        </is>
+      </c>
+      <c r="B46" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C46" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="71" t="n"/>
+      <c r="E46" s="72">
+        <f>C46*D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="33.75" customHeight="1" s="59">
+      <c r="A47" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 6 (6x)</t>
+        </is>
+      </c>
+      <c r="B47" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C47" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="71" t="n"/>
+      <c r="E47" s="72">
+        <f>C47*D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="33.75" customHeight="1" s="59">
+      <c r="A48" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines de 8 (8x)</t>
+        </is>
+      </c>
+      <c r="B48" s="69" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+        </is>
+      </c>
+      <c r="C48" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="71" t="n"/>
+      <c r="E48" s="72">
+        <f>C48*D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 10/10/2026. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1" s="59">
+      <c r="A49" s="68" t="inlineStr">
+        <is>
+          <t>Zócalo DIP de 6 patas</t>
+        </is>
+      </c>
+      <c r="B49" s="69" t="inlineStr">
+        <is>
+          <t>Permite cambiar un relé LCA110 sin desoldar</t>
+        </is>
+      </c>
+      <c r="C49" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="71" t="n"/>
+      <c r="E49" s="72">
+        <f>C49*D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026: el relé va enchufado en el zócalo, con la muesca del lado de la pata 1. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1" s="59">
+      <c r="A50" s="68" t="inlineStr">
+        <is>
+          <t>Resistencia de protección (220 Ω 2 W o 470 Ω 3 W)</t>
+        </is>
+      </c>
+      <c r="B50" s="69" t="inlineStr">
+        <is>
+          <t>Lado del telar: limita la corriente si hay un error de cableado. Va del + del conector del lector a la pata 4 del relé</t>
+        </is>
+      </c>
+      <c r="C50" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="71" t="n"/>
+      <c r="E50" s="72">
+        <f>C50*D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final (la más segura). 220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V: se elige con la medición. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1" s="59">
+      <c r="A51" s="68" t="inlineStr">
+        <is>
+          <t>Resistencia 10 kΩ ½ W</t>
+        </is>
+      </c>
+      <c r="B51" s="69" t="inlineStr">
+        <is>
+          <t>Lado del telar: de la señal al − de cada conector de lector. Con el relé abierto deja la señal en 0 V, como con papel</t>
+        </is>
+      </c>
+      <c r="C51" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="71" t="n"/>
+      <c r="E51" s="72">
+        <f>C51*D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final. Una por canal. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" s="59">
+      <c r="A52" s="68" t="inlineStr">
+        <is>
+          <t>Borneras de 4 vías</t>
+        </is>
+      </c>
+      <c r="B52" s="69" t="inlineStr">
+        <is>
+          <t>Conector de cada lector en la plaqueta del telar, y para dejar aislados los cables del lector</t>
+        </is>
+      </c>
+      <c r="C52" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="72">
+        <f>C52*D52</f>
+        <v/>
+      </c>
+      <c r="F52" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final. Por canal: una para el conector del lector y otra para dejar aislados y rotulados sus 4 cables, que se vuelven a conectar en minutos. Precio a completar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" s="59">
+      <c r="A53" s="111" t="n"/>
+      <c r="B53" s="112" t="inlineStr">
         <is>
           <t>Subtotal bloque</t>
         </is>
       </c>
-      <c r="C44" s="87" t="n"/>
-      <c r="D44" s="88" t="n"/>
-      <c r="E44" s="113">
-        <f>SUM(E38:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="114" t="n"/>
-      <c r="G44" s="115" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1" s="59"/>
-    <row r="46" ht="24" customHeight="1" s="59">
-      <c r="A46" s="116" t="inlineStr">
+      <c r="C53" s="87" t="n"/>
+      <c r="D53" s="88" t="n"/>
+      <c r="E53" s="113">
+        <f>SUM(E38:E52)</f>
+        <v/>
+      </c>
+      <c r="F53" s="114" t="n"/>
+      <c r="G53" s="115" t="n"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="59"/>
+    <row r="55" ht="24" customHeight="1" s="59">
+      <c r="A55" s="116" t="inlineStr">
         <is>
           <t>TOTAL DEL PROYECTO COMPLETO (A + C + D)</t>
         </is>
       </c>
-      <c r="B46" s="117" t="n"/>
-      <c r="C46" s="118" t="n"/>
-      <c r="D46" s="118" t="n"/>
-      <c r="E46" s="119">
-        <f>E21+E34+E44</f>
-        <v/>
-      </c>
-      <c r="F46" s="120" t="n"/>
-      <c r="G46" s="121" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="59"/>
-    <row r="48" ht="21.75" customHeight="1" s="59">
-      <c r="A48" s="122" t="inlineStr">
-        <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la salida de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, cuya conexión (serie o paralelo) depende de esa medición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="59"/>
-    <row r="50" ht="15" customHeight="1" s="59"/>
-    <row r="51" ht="15" customHeight="1" s="59"/>
-    <row r="52" ht="15" customHeight="1" s="59">
-      <c r="A52" s="58" t="n"/>
-      <c r="C52" s="58" t="n"/>
-      <c r="F52" s="58" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="59"/>
-    <row r="54" ht="15" customHeight="1" s="59">
-      <c r="A54" s="58" t="n"/>
-      <c r="F54" s="58" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="59"/>
-    <row r="56" ht="15.75" customHeight="1" s="59">
-      <c r="A56" s="58" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="59">
-      <c r="A57" s="58" t="n"/>
+      <c r="B55" s="117" t="n"/>
+      <c r="C55" s="118" t="n"/>
+      <c r="D55" s="118" t="n"/>
+      <c r="E55" s="119">
+        <f>E21+E34+E53</f>
+        <v/>
+      </c>
+      <c r="F55" s="120" t="n"/>
+      <c r="G55" s="121" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="59"/>
+    <row r="57" ht="21.75" customHeight="1" s="59">
+      <c r="A57" s="122" t="inlineStr">
+        <is>
+          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la alimentación y la señal de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59"/>
-    <row r="59" ht="15.75" customHeight="1" s="59"/>
-    <row r="60" ht="15.75" customHeight="1" s="59"/>
-    <row r="61" ht="15.75" customHeight="1" s="59"/>
-    <row r="62" ht="15.75" customHeight="1" s="59"/>
-    <row r="63" ht="15.75" customHeight="1" s="59"/>
-    <row r="64" ht="15.75" customHeight="1" s="59"/>
-    <row r="65" ht="15.75" customHeight="1" s="59"/>
-    <row r="66" ht="15.75" customHeight="1" s="59"/>
+    <row r="59" ht="15" customHeight="1" s="59"/>
+    <row r="60" ht="15" customHeight="1" s="59"/>
+    <row r="61" ht="15" customHeight="1" s="59">
+      <c r="A61" s="58" t="n"/>
+      <c r="C61" s="58" t="n"/>
+      <c r="F61" s="58" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="59"/>
+    <row r="63" ht="15" customHeight="1" s="59">
+      <c r="A63" s="58" t="n"/>
+      <c r="F63" s="58" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="59"/>
+    <row r="65" ht="15.75" customHeight="1" s="59">
+      <c r="A65" s="58" t="n"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="59">
+      <c r="A66" s="58" t="n"/>
+    </row>
     <row r="67" ht="15.75" customHeight="1" s="59"/>
     <row r="68" ht="15.75" customHeight="1" s="59"/>
     <row r="69" ht="15.75" customHeight="1" s="59"/>
@@ -3271,25 +3532,25 @@
     <row r="1003" ht="15.75" customHeight="1" s="59"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F63:G63"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A57:B60"/>
     <mergeCell ref="A2:G3"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="H4:Z248"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="A48:B51"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="H1:Z3"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="H4:Z252"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <hyperlinks>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B11" s="76" t="inlineStr">
         <is>
-          <t>Limita la corriente hacia el LED del PC817. Es el valor para una botonera de 18 a 24 V: si al medirla diera entre 12 y 18 V, va de 1,2 kΩ.</t>
+          <t>Limita la corriente hacia el LED del PC817. Es el valor para una botonera de 18 a 24 V: si al medirla diera entre 12 y 18 V, va de 1,2 kΩ 1 W.</t>
         </is>
       </c>
       <c r="C11" s="77" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B13" s="69" t="inlineStr">
         <is>
-          <t>Relés: pull-up en IN1 e IN2, pull-down a GND en IN3 (con pull-up el relé de Retroceder arranca cerrado). Sensado: pull-up en GPIO 32, 33 y 34 (Marcha, Pausa, Retroceder)</t>
+          <t>Relés: pull-up en IN1 e IN2, pull-down a GND en S, la entrada del módulo de Retroceder (con pull-up arranca cerrado). Sensado: pull-up en GPIO 32, 33 y 34 (Marcha, Pausa, Retroceder)</t>
         </is>
       </c>
       <c r="C13" s="70" t="n">
@@ -1616,15 +1616,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="59">
+    <row r="20" ht="51.25" customHeight="1" s="59">
       <c r="A20" s="68" t="inlineStr">
         <is>
-          <t>Capacitor electrolítico 22–47 µF 50 V</t>
-        </is>
-      </c>
-      <c r="B20" s="76" t="inlineStr">
-        <is>
-          <t>Aplana el AC rectificado antes del optoacoplador</t>
+          <t>Capacitor electrolítico 22 µF 50 V</t>
+        </is>
+      </c>
+      <c r="B20" s="69" t="inlineStr">
+        <is>
+          <t>Mantiene encendido el LED del optoacoplador entre los semiciclos del rectificado</t>
         </is>
       </c>
       <c r="C20" s="70" t="n">
@@ -1642,9 +1642,9 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G20" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sin él, el sensado lee varias pulsaciones donde hubo una sola: es crítico en el canal de Retroceder.</t>
+      <c r="G20" s="74" t="inlineStr">
+        <is>
+          <t>Sin él, el sensado manda avisos solos, sin que nadie apriete nada: es crítico en el canal de Retroceder. Con 47 µF un toque rápido del botón no se registra.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1723,7 +1723,7 @@
       </c>
       <c r="B25" s="69" t="inlineStr">
         <is>
-          <t>Sensor de pasada recomendado, inmune a la pelusa. Incluye 1 repuesto, esto es lo que le da al ESP32 el "entendimiento" de movimiento y posición del telar</t>
+          <t>Sensor de pasada recomendado, inmune a la pelusa. Es lo que le da al ESP32 el "entendimiento" de movimiento y posición del telar</t>
         </is>
       </c>
       <c r="C25" s="70" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G26" s="58" t="inlineStr">
         <is>
-          <t>El error que no podés cometer es pasarte de 36, y el regulador lo hace imposible. El otro extremo no tiene consecuencia.</t>
+          <t>No se usa: el telar da 12 a 14 V continuos, dentro del rango del sensor (6 a 36 V).</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G33" s="101" t="inlineStr">
         <is>
-          <t>A fabricar: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
+          <t>Ya construido y montado el 10/09/2026: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
     <row r="57" ht="21.75" customHeight="1" s="59">
       <c r="A57" s="122" t="inlineStr">
         <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A ahora, para la Etapa 4. (2) Medición de la alimentación y la señal de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
+          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1120,7 +1120,7 @@
     <row r="4" ht="19.5" customHeight="1" s="59">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>BLOQUE A, Nivel 1: Marcha, Pausa y Retroceder en el telar  (Etapa 4)</t>
+          <t>BLOQUE A, Nivel 1: Marcha, Pausa y Retroceder en el telar (Etapa 4)</t>
         </is>
       </c>
       <c r="B4" s="63" t="n"/>
@@ -1203,7 +1203,7 @@
     <row r="7" ht="48.75" customHeight="1" s="59">
       <c r="A7" s="68" t="inlineStr">
         <is>
-          <t>Módulos de relé, 3 canales en total (5V, optoacoplado)</t>
+          <t>Módulos de relé, 3 canales en total (5V; el de 2 canales, optoacoplado)</t>
         </is>
       </c>
       <c r="B7" s="69" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B14" s="69" t="inlineStr">
         <is>
-          <t>Sostienen ante un consumo brusco</t>
+          <t>Sostiene los 5 V ante un consumo brusco</t>
         </is>
       </c>
       <c r="C14" s="70" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F15" s="73" t="inlineStr">
         <is>
-          <t>https://candy-ho.com/producto/tiras-de-40-pines-hembra-paso-2-54mm-recta-1-fila-arduino/   -  https://candy-ho.com/producto/pcb-placa-experimental-doble-7x9-prototipos-electronica-fr4/</t>
+          <t>https://candy-ho.com/producto/tiras-de-40-pines-hembra-paso-2-54mm-recta-1-fila-arduino/ - https://candy-ho.com/producto/pcb-placa-experimental-doble-7x9-prototipos-electronica-fr4/</t>
         </is>
       </c>
       <c r="G15" s="74" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="19" ht="45.75" customHeight="1" s="59">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable multifilar 6 conductores, 1 mm² </t>
+          <t xml:space="preserve">Cable multifilar 6 conductores, 1 mm²</t>
         </is>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="23" ht="18.75" customHeight="1" s="59">
       <c r="A23" s="92" t="inlineStr">
         <is>
-          <t>BLOQUE C, Sensor de pasada  (INCLUIDO EN ESTA ETAPA)</t>
+          <t>BLOQUE C, Sensor de pasada (INCLUIDO EN ESTA ETAPA)</t>
         </is>
       </c>
       <c r="B23" s="93" t="n"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G39" s="101" t="inlineStr">
         <is>
-          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1, TLP3021 (cada uno con su propia disposición de patas). Conexión final: el relé en lugar del lector, con una resistencia de protección (diagramas/hardware/conexion_final_rele.png). Comprar 1 y probarlo antes de los otros 3.</t>
+          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1 (cada uno con su propia disposición de patas). Conexión final: el relé en lugar del lector, con una resistencia de protección (diagramas/hardware/conexion_final_rele.png). Comprar 1 y probarlo antes de los otros 3.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -2445,7 +2445,7 @@
     <row r="50" ht="60" customHeight="1" s="59">
       <c r="A50" s="68" t="inlineStr">
         <is>
-          <t>Resistencia de protección (220 Ω 2 W o 470 Ω 3 W)</t>
+          <t>Resistencia de protección 470 Ω 3 W</t>
         </is>
       </c>
       <c r="B50" s="69" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="G50" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 11/10/2026 con la conexión final (la más segura). 220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V: se elige con la medición. Precio a completar.</t>
+          <t>Se suma el 11/10/2026 con la conexión final (la más segura). 220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V: se elige con la medición. En el C 201 dio entre 15 y 30 V (17/10/2026): van las de 470 Ω 3 W. Precio a completar.</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
     <row r="57" ht="21.75" customHeight="1" s="59">
       <c r="A57" s="122" t="inlineStr">
         <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 10/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard y funcionó; se está haciendo la plaqueta para la prueba definitiva.</t>
+          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 17/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard el 10/10/2026 y en el telar el 17/10/2026, con el sensor y el primer canal: funcionó; se están haciendo las plaquetas para la instalación definitiva.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -490,7 +490,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -840,6 +840,30 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1168,7 +1192,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1" s="59">
+    <row r="6" ht="47" customHeight="1" s="59">
       <c r="A6" s="68" t="inlineStr">
         <is>
           <t>ESP32 (NodeMCU / WROOM-32)</t>
@@ -1189,7 +1213,7 @@
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="73" t="inlineStr">
+      <c r="F6" s="123" t="inlineStr">
         <is>
           <t>https://candy-ho.com/producto/nodemcu-esp32-wifi-bluetooth-4-2-iot-wroom-esp32s-arduino/</t>
         </is>
@@ -1201,7 +1225,7 @@
       </c>
     </row>
     <row r="7" ht="48.75" customHeight="1" s="59">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="124" t="inlineStr">
         <is>
           <t>Módulos de relé, 3 canales en total (5V; el de 2 canales, optoacoplado)</t>
         </is>
@@ -1221,7 +1245,7 @@
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="73" t="inlineStr">
+      <c r="F7" s="123" t="inlineStr">
         <is>
           <t>https://candy-ho.com/producto/modulo-relay-rele-de-2-canales-5v-10a-arduino-pic-avr-2/</t>
         </is>
@@ -1232,24 +1256,24 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="59">
-      <c r="A8" s="75" t="inlineStr">
+    <row r="8" ht="32.5" customHeight="1" s="59">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>Módulo fuente HLK-5M05 (220V→5V, 1A)</t>
         </is>
       </c>
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="125" t="inlineStr">
         <is>
           <t>Alimenta ESP32 + relés + sensado, independiente del telar</t>
         </is>
       </c>
-      <c r="C8" s="77" t="n">
+      <c r="C8" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="78" t="n">
+      <c r="D8" s="71" t="n">
         <v>7000</v>
       </c>
-      <c r="E8" s="79">
+      <c r="E8" s="72">
         <f>C8*D8</f>
         <v/>
       </c>
@@ -1264,24 +1288,24 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="59">
-      <c r="A9" s="75" t="inlineStr">
+    <row r="9" ht="32.5" customHeight="1" s="59">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>Optoacoplador PC817</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="125" t="inlineStr">
         <is>
           <t>Aísla el 24V AC del botón del GPIO del ESP32, uno por canal</t>
         </is>
       </c>
-      <c r="C9" s="77" t="n">
+      <c r="C9" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="78" t="n">
+      <c r="D9" s="71" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="79">
+      <c r="E9" s="72">
         <f>C9*D9</f>
         <v/>
       </c>
@@ -1296,24 +1320,24 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="59">
-      <c r="A10" s="75" t="inlineStr">
+    <row r="10" ht="32.5" customHeight="1" s="59">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>Puente rectificador DB157 (1A)</t>
         </is>
       </c>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="125" t="inlineStr">
         <is>
           <t>Convierte el 24V AC del botón en pulsos de DC, antes del PC817</t>
         </is>
       </c>
-      <c r="C10" s="77" t="n">
+      <c r="C10" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="78" t="n">
+      <c r="D10" s="71" t="n">
         <v>500</v>
       </c>
-      <c r="E10" s="79">
+      <c r="E10" s="72">
         <f>C10*D10</f>
         <v/>
       </c>
@@ -1328,24 +1352,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="59">
-      <c r="A11" s="75" t="inlineStr">
+    <row r="11" ht="47" customHeight="1" s="59">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>Resistencia 2,2kΩ 1W</t>
         </is>
       </c>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="125" t="inlineStr">
         <is>
           <t>Limita la corriente hacia el LED del PC817. Es el valor para una botonera de 18 a 24 V: si al medirla diera entre 12 y 18 V, va de 1,2 kΩ 1 W.</t>
         </is>
       </c>
-      <c r="C11" s="77" t="n">
+      <c r="C11" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="81" t="n">
+      <c r="D11" s="126" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="82">
+      <c r="E11" s="127">
         <f>C11*D11</f>
         <v/>
       </c>
@@ -1392,7 +1416,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30.75" customHeight="1" s="59">
+    <row r="13" ht="61.75" customHeight="1" s="59">
       <c r="A13" s="68" t="inlineStr">
         <is>
           <t>Resistencias 10kΩ ¼W</t>
@@ -1424,7 +1448,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45.75" customHeight="1" s="59">
+    <row r="14" ht="70.25" customHeight="1" s="59">
       <c r="A14" s="68" t="inlineStr">
         <is>
           <t>Capacitor electrolítico de 220 a 470 µF</t>
@@ -1450,13 +1474,13 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G14" s="83" t="inlineStr">
+      <c r="G14" s="128" t="inlineStr">
         <is>
           <t>Cuando la bobina de un relé engancha tira unos 70 mA de golpe, y si en ese instante el ESP32 está transmitiendo por WiFi (que le pide picos de hasta 300 mA), la fuente no responde lo bastante rápido y la tensión cae lo suficiente para reiniciarlo.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="45.75" customHeight="1" s="59">
+    <row r="15" ht="91" customHeight="1" s="59">
       <c r="A15" s="68" t="inlineStr">
         <is>
           <t>Protoboard de ensayo y cables</t>
@@ -1477,7 +1501,7 @@
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="73" t="inlineStr">
+      <c r="F15" s="123" t="inlineStr">
         <is>
           <t>https://candy-ho.com/producto/tiras-de-40-pines-hembra-paso-2-54mm-recta-1-fila-arduino/ - https://candy-ho.com/producto/pcb-placa-experimental-doble-7x9-prototipos-electronica-fr4/</t>
         </is>
@@ -1488,7 +1512,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="59">
+    <row r="16" ht="32.5" customHeight="1" s="59">
       <c r="A16" s="68" t="inlineStr">
         <is>
           <t>Caja estanca IP65 Roker 230x300x106mm</t>
@@ -1552,7 +1576,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="59">
+    <row r="18" ht="32.5" customHeight="1" s="59">
       <c r="A18" s="68" t="inlineStr">
         <is>
           <t>Fusible 1A lento + portafusible</t>
@@ -1587,7 +1611,7 @@
     <row r="19" ht="45.75" customHeight="1" s="59">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable multifilar 6 conductores, 1 mm²</t>
+          <t>Cable multifilar 6 conductores, 1 mm²</t>
         </is>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -1616,7 +1640,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="51.25" customHeight="1" s="59">
+    <row r="20" ht="61.75" customHeight="1" s="59">
       <c r="A20" s="68" t="inlineStr">
         <is>
           <t>Capacitor electrolítico 22 µF 50 V</t>
@@ -1630,7 +1654,7 @@
       <c r="C20" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="78" t="n">
+      <c r="D20" s="71" t="n">
         <v>400</v>
       </c>
       <c r="E20" s="72">
@@ -1747,13 +1771,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="29.25" customHeight="1" s="59">
+    <row r="26" ht="47" customHeight="1" s="59">
       <c r="A26" s="68" t="inlineStr">
         <is>
           <t>(no aplica) Regulador 7824</t>
         </is>
       </c>
-      <c r="B26" s="99" t="inlineStr">
+      <c r="B26" s="129" t="inlineStr">
         <is>
           <t>Ya no es necesario: el telar entrega 12 a 14 V continuos, muy por debajo de los 36 V que tolera el sensor</t>
         </is>
@@ -1773,19 +1797,19 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G26" s="58" t="inlineStr">
+      <c r="G26" s="128" t="inlineStr">
         <is>
           <t>No se usa: el telar da 12 a 14 V continuos, dentro del rango del sensor (6 a 36 V).</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="29.25" customHeight="1" s="59">
+    <row r="27" ht="32.5" customHeight="1" s="59">
       <c r="A27" s="68" t="inlineStr">
         <is>
           <t>Optoacoplador PC817</t>
         </is>
       </c>
-      <c r="B27" s="99" t="inlineStr">
+      <c r="B27" s="129" t="inlineStr">
         <is>
           <t>Aísla la señal del sensor inductivo (hasta 36V) del GPIO del ESP32</t>
         </is>
@@ -1805,19 +1829,19 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G27" s="100" t="inlineStr">
+      <c r="G27" s="130" t="inlineStr">
         <is>
           <t>Uno en uso y uno de repuesto. Mismo componente que el sensado del Bloque A.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1" s="59">
+    <row r="28" ht="32.5" customHeight="1" s="59">
       <c r="A28" s="68" t="inlineStr">
         <is>
           <t>(no aplica) Puente rectificador DB157</t>
         </is>
       </c>
-      <c r="B28" s="80" t="inlineStr">
+      <c r="B28" s="125" t="inlineStr">
         <is>
           <t>Ya no es necesario para este bloque: la alimentación del sensor ya viene en continua</t>
         </is>
@@ -1843,7 +1867,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="22.5" customHeight="1" s="59">
+    <row r="29" ht="61.75" customHeight="1" s="59">
       <c r="A29" s="68" t="inlineStr">
         <is>
           <t>Cable 3 conectores (para sensor inductivo)</t>
@@ -1875,7 +1899,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="22.5" customHeight="1" s="59">
+    <row r="30" ht="32.5" customHeight="1" s="59">
       <c r="A30" s="68" t="inlineStr">
         <is>
           <t>Resistencia 1,2 kΩ ¼ W</t>
@@ -1907,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="28.5" customHeight="1" s="59">
+    <row r="31" ht="32.5" customHeight="1" s="59">
       <c r="A31" s="68" t="inlineStr">
         <is>
           <t>Resistencia 10kΩ ¼W</t>
@@ -1933,13 +1957,13 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G31" s="100" t="inlineStr">
+      <c r="G31" s="130" t="inlineStr">
         <is>
           <t>Mantiene el pin del ESP32 en nivel alto mientras el sensor no detecta.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="25.5" customHeight="1" s="59">
+    <row r="32" ht="32.5" customHeight="1" s="59">
       <c r="A32" s="68" t="inlineStr">
         <is>
           <t>(no aplica) Capacitor cerámico 100 nF</t>
@@ -1965,13 +1989,13 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G32" s="100" t="inlineStr">
+      <c r="G32" s="130" t="inlineStr">
         <is>
           <t>No se usa: acompañaba al regulador 7824, que se descartó.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="51.75" customHeight="1" s="59">
+    <row r="33" ht="61.75" customHeight="1" s="59">
       <c r="A33" s="68" t="inlineStr">
         <is>
           <t>Blanco metálico y soporte</t>
@@ -2070,7 +2094,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="48" customHeight="1" s="59">
+    <row r="38" ht="76.25" customHeight="1" s="59">
       <c r="A38" s="68" t="inlineStr">
         <is>
           <t>Bobinas de selección del telar (YA INSTALADAS)</t>
@@ -2102,7 +2126,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1" s="59">
+    <row r="39" ht="252" customHeight="1" s="59">
       <c r="A39" s="68" t="inlineStr">
         <is>
           <t>Relé OptoMOS LCA110 de IXYS (DIP-6)</t>
@@ -2134,7 +2158,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="33.75" customHeight="1" s="59">
+    <row r="40" ht="47" customHeight="1" s="59">
       <c r="A40" s="68" t="inlineStr">
         <is>
           <t>Borneras atornillables chicas</t>
@@ -2160,7 +2184,7 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G40" s="100" t="inlineStr">
+      <c r="G40" s="130" t="inlineStr">
         <is>
           <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos. Las del conector de cada lector son las de 4 vías (abajo).</t>
         </is>
@@ -2172,7 +2196,7 @@
           <t>Cable para los 4 canales</t>
         </is>
       </c>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="B41" s="125" t="inlineStr">
         <is>
           <t>Conexión entre el gabinete y el conector de cada lector</t>
         </is>
@@ -2192,7 +2216,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="100" t="inlineStr">
+      <c r="G41" s="130" t="inlineStr">
         <is>
           <t>Se aprovecha el sobrante del cable del Bloque A. Cantidad a definir según el recorrido real.</t>
         </is>
@@ -2230,13 +2254,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="21.75" customHeight="1" s="59">
+    <row r="43" ht="61.75" customHeight="1" s="59">
       <c r="A43" s="68" t="inlineStr">
         <is>
           <t>Resistencia 330 Ω ¼ W</t>
         </is>
       </c>
-      <c r="B43" s="80" t="inlineStr">
+      <c r="B43" s="125" t="inlineStr">
         <is>
           <t>Limita la corriente del LED de entrada de cada relé LCA110</t>
         </is>
@@ -2256,13 +2280,13 @@
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G43" s="100" t="inlineStr">
+      <c r="G43" s="130" t="inlineStr">
         <is>
           <t>Una por canal. Con los 3,3 V del ESP32 entrega unos 6 mA. NO es opcional: sin ella se daña el LED del relé. El SSR de triac no la necesita porque la trae incorporada.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="45" customHeight="1" s="59">
+    <row r="44" ht="61.75" customHeight="1" s="59">
       <c r="A44" s="68" t="inlineStr">
         <is>
           <t>Placa experimental (plaqueta) adicional</t>
@@ -2442,7 +2466,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1" s="59">
+    <row r="50" ht="91" customHeight="1" s="59">
       <c r="A50" s="68" t="inlineStr">
         <is>
           <t>Resistencia de protección 470 Ω 3 W</t>
@@ -2502,7 +2526,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1" s="59">
+    <row r="52" ht="76.25" customHeight="1" s="59">
       <c r="A52" s="68" t="inlineStr">
         <is>
           <t>Borneras de 4 vías</t>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E6" s="72">
         <f>C6*D6</f>
-        <v/>
+        <v>12203</v>
       </c>
       <c r="F6" s="123" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E7" s="72">
         <f>C7*D7</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="F7" s="123" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E8" s="72">
         <f>C8*D8</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="F8" s="80" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E9" s="72">
         <f>C9*D9</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="F9" s="80" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E10" s="72">
         <f>C10*D10</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="F10" s="80" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E11" s="127">
         <f>C11*D11</f>
-        <v/>
+        <v>450</v>
       </c>
       <c r="F11" s="80" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E12" s="72">
         <f>C12*D12</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="F12" s="80" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E13" s="72">
         <f>C13*D13</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="F13" s="80" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E14" s="72">
         <f>C14*D14</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="F14" s="80" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E15" s="72">
         <f>C15*D15</f>
-        <v/>
+        <v>15000</v>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E16" s="72">
         <f>C16*D16</f>
-        <v/>
+        <v>16000</v>
       </c>
       <c r="F16" s="80" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E17" s="72">
         <f>C17*D17</f>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="F17" s="80" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E18" s="72">
         <f>C18*D18</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="F18" s="80" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E19" s="72">
         <f>C19*D19</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="F19" s="80" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E20" s="72">
         <f>C20*D20</f>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="F20" s="80" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       <c r="D21" s="88" t="n"/>
       <c r="E21" s="89">
         <f>SUM(E6:E20)</f>
-        <v/>
+        <v>73653</v>
       </c>
       <c r="F21" s="90" t="n"/>
       <c r="G21" s="91" t="n"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E25" s="72">
         <f>C25*D25</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="F25" s="98" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E26" s="72">
         <f>C26*D26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F26" s="98" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E27" s="72">
         <f>C27*D27</f>
-        <v/>
+        <v>1400</v>
       </c>
       <c r="F27" s="98" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E28" s="72">
         <f>C28*D28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F28" s="98" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E29" s="72">
         <f>C29*D29</f>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="F29" s="98" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E30" s="72">
         <f>C30*D30</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="F30" s="98" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="E31" s="72">
         <f>C31*D31</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="F31" s="98" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="E32" s="72">
         <f>C32*D32</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F32" s="98" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E33" s="72">
         <f>C33*D33</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F33" s="98" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
       <c r="D34" s="88" t="n"/>
       <c r="E34" s="103">
         <f>SUM(E25:E33)</f>
-        <v/>
+        <v>13950</v>
       </c>
       <c r="F34" s="104" t="n"/>
       <c r="G34" s="90" t="n"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E38" s="72">
         <f>C38*D38</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="98" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E39" s="72">
         <f>C39*D39</f>
-        <v/>
+        <v>24136</v>
       </c>
       <c r="F39" s="98" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E40" s="110">
         <f>C40*D40</f>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="F40" s="98" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E41" s="72">
         <f>C41*D41</f>
-        <v/>
+        <v>5600</v>
       </c>
       <c r="F41" s="98" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="E42" s="72">
         <f>C42*D42</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="F42" s="98" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E43" s="110">
         <f>C43*D43</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="F43" s="98" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
       <c r="D44" s="71" t="n"/>
       <c r="E44" s="72">
         <f>C44*D44</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F44" s="98" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       <c r="D45" s="71" t="n"/>
       <c r="E45" s="72">
         <f>C45*D45</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="98" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
       <c r="D46" s="71" t="n"/>
       <c r="E46" s="72">
         <f>C46*D46</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F46" s="98" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
       <c r="D47" s="71" t="n"/>
       <c r="E47" s="72">
         <f>C47*D47</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="98" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       <c r="D48" s="71" t="n"/>
       <c r="E48" s="72">
         <f>C48*D48</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="98" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
       <c r="D49" s="71" t="n"/>
       <c r="E49" s="72">
         <f>C49*D49</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="98" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       <c r="D50" s="71" t="n"/>
       <c r="E50" s="72">
         <f>C50*D50</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="98" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
       <c r="D51" s="71" t="n"/>
       <c r="E51" s="72">
         <f>C51*D51</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F51" s="98" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       <c r="D52" s="71" t="n"/>
       <c r="E52" s="72">
         <f>C52*D52</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F52" s="98" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       <c r="D53" s="88" t="n"/>
       <c r="E53" s="113">
         <f>SUM(E38:E52)</f>
-        <v/>
+        <v>34536</v>
       </c>
       <c r="F53" s="114" t="n"/>
       <c r="G53" s="115" t="n"/>
@@ -2584,7 +2584,7 @@
       <c r="D55" s="118" t="n"/>
       <c r="E55" s="119">
         <f>E21+E34+E53</f>
-        <v/>
+        <v>122139</v>
       </c>
       <c r="F55" s="120" t="n"/>
       <c r="G55" s="121" t="n"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G44" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 10/10/2026: con todo probado en protoboard, se está haciendo la plaqueta para probar todo de manera correcta. Precio a completar.</t>
+          <t>Se suma el 10/10/2026, con todo probado en protoboard. Ya está soldada (20/10/2026). Precio a completar.</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="57" ht="21.75" customHeight="1" s="59">
       <c r="A57" s="122" t="inlineStr">
         <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 17/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard el 10/10/2026 y en el telar el 17/10/2026, con el sensor y el primer canal: funcionó; se están haciendo las plaquetas para la instalación definitiva.</t>
+          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 20/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard el 10/10/2026 y en el telar el 17/10/2026, con el sensor y el primer canal: funcionó, y al 20/10/2026 las plaquetas para la instalación definitiva ya están soldadas.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1451,7 +1451,7 @@
     <row r="14" ht="70.25" customHeight="1" s="59">
       <c r="A14" s="68" t="inlineStr">
         <is>
-          <t>Capacitor electrolítico de 220 a 470 µF</t>
+          <t>Capacitor electrolítico 470 µF 16 V</t>
         </is>
       </c>
       <c r="B14" s="69" t="inlineStr">

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B13" s="69" t="inlineStr">
         <is>
-          <t>Relés: pull-up en IN1 e IN2, pull-down a GND en S, la entrada del módulo de Retroceder (con pull-up arranca cerrado). Sensado: pull-up en GPIO 32, 33 y 34 (Marcha, Pausa, Retroceder)</t>
+          <t>Relés: pull-up en IN1 e IN2, pull-down a GND en S, la entrada del módulo de Retroceder (con pull-up arranca cerrado). Sensado: pull-up en GPIO 34 (Retroceder); GPIO 32 y 33 (Marcha y Pausa) usan la pull-up interna del ESP32</t>
         </is>
       </c>
       <c r="C13" s="70" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G13" s="74" t="inlineStr">
         <is>
-          <t>Ya se tiene</t>
+          <t>Ya se tiene. 4 en uso y 2 de repuesto.</t>
         </is>
       </c>
     </row>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -1198,7 +1198,7 @@
           <t>ESP32 (NodeMCU / WROOM-32)</t>
         </is>
       </c>
-      <c r="B6" s="69" t="inlineStr">
+      <c r="B6" s="125" t="inlineStr">
         <is>
           <t>El cerebro: recibe órdenes por WiFi y dispara los relés</t>
         </is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E6" s="72">
         <f>C6*D6</f>
-        <v>12203</v>
+        <v/>
       </c>
       <c r="F6" s="123" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
           <t>Módulos de relé, 3 canales en total (5V; el de 2 canales, optoacoplado)</t>
         </is>
       </c>
-      <c r="B7" s="69" t="inlineStr">
+      <c r="B7" s="125" t="inlineStr">
         <is>
           <t>En paralelo a los botones Marcha, Pausa y Retroceder del telar</t>
         </is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E7" s="72">
         <f>C7*D7</f>
-        <v>5000</v>
+        <v/>
       </c>
       <c r="F7" s="123" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E8" s="72">
         <f>C8*D8</f>
-        <v>7000</v>
+        <v/>
       </c>
       <c r="F8" s="80" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E9" s="72">
         <f>C9*D9</f>
-        <v>1500</v>
+        <v/>
       </c>
       <c r="F9" s="80" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E10" s="72">
         <f>C10*D10</f>
-        <v>1500</v>
+        <v/>
       </c>
       <c r="F10" s="80" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E11" s="127">
         <f>C11*D11</f>
-        <v>450</v>
+        <v/>
       </c>
       <c r="F11" s="80" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
           <t>Capacitores cerámicos 100nF</t>
         </is>
       </c>
-      <c r="B12" s="69" t="inlineStr">
+      <c r="B12" s="125" t="inlineStr">
         <is>
           <t>Filtran ruido de alta frecuencia</t>
         </is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E12" s="72">
         <f>C12*D12</f>
-        <v>900</v>
+        <v/>
       </c>
       <c r="F12" s="80" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
           <t>Resistencias 10kΩ ¼W</t>
         </is>
       </c>
-      <c r="B13" s="69" t="inlineStr">
+      <c r="B13" s="125" t="inlineStr">
         <is>
           <t>Relés: pull-up en IN1 e IN2, pull-down a GND en S, la entrada del módulo de Retroceder (con pull-up arranca cerrado). Sensado: pull-up en GPIO 34 (Retroceder); GPIO 32 y 33 (Marcha y Pausa) usan la pull-up interna del ESP32</t>
         </is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E13" s="72">
         <f>C13*D13</f>
-        <v>900</v>
+        <v/>
       </c>
       <c r="F13" s="80" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
           <t>Capacitor electrolítico 470 µF 16 V</t>
         </is>
       </c>
-      <c r="B14" s="69" t="inlineStr">
+      <c r="B14" s="125" t="inlineStr">
         <is>
           <t>Sostiene los 5 V ante un consumo brusco</t>
         </is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E14" s="72">
         <f>C14*D14</f>
-        <v>300</v>
+        <v/>
       </c>
       <c r="F14" s="80" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
           <t>Protoboard de ensayo y cables</t>
         </is>
       </c>
-      <c r="B15" s="69" t="inlineStr">
+      <c r="B15" s="125" t="inlineStr">
         <is>
           <t>Montaje y conexionado</t>
         </is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E15" s="72">
         <f>C15*D15</f>
-        <v>15000</v>
+        <v/>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
           <t>Caja estanca IP65 Roker 230x300x106mm</t>
         </is>
       </c>
-      <c r="B16" s="69" t="inlineStr">
+      <c r="B16" s="125" t="inlineStr">
         <is>
           <t>Gabinete del ESP32, relés y fuente, montado junto al telar</t>
         </is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E16" s="72">
         <f>C16*D16</f>
-        <v>16000</v>
+        <v/>
       </c>
       <c r="F16" s="80" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
           <t>Prensacables PG11</t>
         </is>
       </c>
-      <c r="B17" s="69" t="inlineStr">
+      <c r="B17" s="125" t="inlineStr">
         <is>
           <t>Entrada/salida de cables sin romper el sellado IP65</t>
         </is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E17" s="72">
         <f>C17*D17</f>
-        <v>3200</v>
+        <v/>
       </c>
       <c r="F17" s="80" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
           <t>Fusible 1A lento + portafusible</t>
         </is>
       </c>
-      <c r="B18" s="69" t="inlineStr">
+      <c r="B18" s="125" t="inlineStr">
         <is>
           <t>Protege la entrada de 220V del HLK-5M05 (su datasheet pide 1A)</t>
         </is>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E18" s="72">
         <f>C18*D18</f>
-        <v>1000</v>
+        <v/>
       </c>
       <c r="F18" s="80" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
           <t>Cable multifilar 6 conductores, 1 mm²</t>
         </is>
       </c>
-      <c r="B19" s="69" t="inlineStr">
+      <c r="B19" s="125" t="inlineStr">
         <is>
           <t>Marcha + Pausa + Retroceder</t>
         </is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E19" s="72">
         <f>C19*D19</f>
-        <v>7500</v>
+        <v/>
       </c>
       <c r="F19" s="80" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
           <t>Capacitor electrolítico 22 µF 50 V</t>
         </is>
       </c>
-      <c r="B20" s="69" t="inlineStr">
+      <c r="B20" s="125" t="inlineStr">
         <is>
           <t>Mantiene encendido el LED del optoacoplador entre los semiciclos del rectificado</t>
         </is>
@@ -1659,298 +1659,298 @@
       </c>
       <c r="E20" s="72">
         <f>C20*D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="80" t="inlineStr">
+        <is>
+          <t>Comprado en el local</t>
+        </is>
+      </c>
+      <c r="G20" s="74" t="inlineStr">
+        <is>
+          <t>Sin él, el sensado manda avisos solos, sin que nadie apriete nada: es crítico en el canal de Retroceder. Con 47 µF un toque rápido del botón no se registra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="61.75" customHeight="1" s="59">
+      <c r="A21" s="68" t="inlineStr">
+        <is>
+          <t>Placa para la plaqueta del ESP32</t>
+        </is>
+      </c>
+      <c r="B21" s="125" t="inlineStr">
+        <is>
+          <t>Lleva el ESP32 en sus tiras hembra y saca sus señales a P1 y P2, que se cablean a la plaqueta principal</t>
+        </is>
+      </c>
+      <c r="C21" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="71" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="72">
+        <f>C21*D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 25/10/2026: en la principal impresa, la tira derecha del ESP32 quedó con los pines en otro orden (J5 y J7 invertidos) y el ESP32 no se puede enchufar ahí. De una sola cara y sin puentes (diagramas/hardware/plaqueta_esp32). Precio estimado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="47" customHeight="1" s="59">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines hembra 1×40 (se corta en dos de 19)</t>
+        </is>
+      </c>
+      <c r="B22" s="125" t="inlineStr">
+        <is>
+          <t>Zócalo del ESP32 de 38 pines en la plaqueta del ESP32: así se cambia sin desoldar</t>
+        </is>
+      </c>
+      <c r="C22" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="71" t="n">
         <v>1200</v>
       </c>
-      <c r="F20" s="80" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G20" s="74" t="inlineStr">
-        <is>
-          <t>Sin él, el sensado manda avisos solos, sin que nadie apriete nada: es crítico en el canal de Retroceder. Con 47 µF un toque rápido del botón no se registra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1" s="59">
-      <c r="A21" s="85" t="n"/>
-      <c r="B21" s="86" t="inlineStr">
-        <is>
-          <t>Subtotal bloque</t>
-        </is>
-      </c>
-      <c r="C21" s="87" t="n"/>
-      <c r="D21" s="88" t="n"/>
-      <c r="E21" s="89">
-        <f>SUM(E6:E20)</f>
-        <v>73653</v>
-      </c>
-      <c r="F21" s="90" t="n"/>
-      <c r="G21" s="91" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="59"/>
-    <row r="23" ht="18.75" customHeight="1" s="59">
-      <c r="A23" s="92" t="inlineStr">
-        <is>
-          <t>BLOQUE C, Sensor de pasada (INCLUIDO EN ESTA ETAPA)</t>
-        </is>
-      </c>
-      <c r="B23" s="93" t="n"/>
-      <c r="C23" s="93" t="n"/>
-      <c r="D23" s="93" t="n"/>
-      <c r="E23" s="93" t="n"/>
-      <c r="F23" s="93" t="n"/>
-      <c r="G23" s="94" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="59">
-      <c r="A24" s="95" t="inlineStr">
-        <is>
-          <t>Componente</t>
-        </is>
-      </c>
-      <c r="B24" s="96" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="C24" s="96" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="D24" s="96" t="inlineStr">
-        <is>
-          <t>Precio unit.</t>
-        </is>
-      </c>
-      <c r="E24" s="96" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="F24" s="96" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="G24" s="97" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="53.25" customHeight="1" s="59">
+      <c r="E22" s="72">
+        <f>C22*D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="74" t="inlineStr">
+        <is>
+          <t>Las dos tiras van a 25,4 mm, con el pin 1 del lado de la antena. Medir el módulo antes de soldar. Precio estimado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="47" customHeight="1" s="59">
+      <c r="A23" s="68" t="inlineStr">
+        <is>
+          <t>Tira de pines macho 1×40 (P1 de 10 y P2 de 5)</t>
+        </is>
+      </c>
+      <c r="B23" s="125" t="inlineStr">
+        <is>
+          <t>Salidas de la plaqueta del ESP32 hacia la principal</t>
+        </is>
+      </c>
+      <c r="C23" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="71" t="n">
+        <v>600</v>
+      </c>
+      <c r="E23" s="72">
+        <f>C23*D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="74" t="inlineStr">
+        <is>
+          <t>P1: 3V3, IO34, IO35, IO32, IO33, IO25, IO26, IO27, GND y 5V. P2: IO22, IO21, GND, IO19 e IO18. Precio estimado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="47" customHeight="1" s="59">
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>Cables dupont hembra (paquete de 40)</t>
+        </is>
+      </c>
+      <c r="B24" s="125" t="inlineStr">
+        <is>
+          <t>Unen P1 y P2 con los pads de la principal, cada uno por nombre de señal</t>
+        </is>
+      </c>
+      <c r="C24" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="71" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="72">
+        <f>C24*D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="74" t="inlineStr">
+        <is>
+          <t>Se usan 15: hembra en P1/P2 y el otro extremo soldado al pad de la principal. Colores fijos: rojo 5V, naranja 3V3, negro GND. Precio estimado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="47" customHeight="1" s="59">
       <c r="A25" s="68" t="inlineStr">
         <is>
-          <t>Sensor inductivo LJ12A3-4-Z/BX (NPN 6–36V)</t>
-        </is>
-      </c>
-      <c r="B25" s="69" t="inlineStr">
-        <is>
-          <t>Sensor de pasada recomendado, inmune a la pelusa. Es lo que le da al ESP32 el "entendimiento" de movimiento y posición del telar</t>
+          <t>Alambre aislado para puentes</t>
+        </is>
+      </c>
+      <c r="B25" s="125" t="inlineStr">
+        <is>
+          <t>Reemplaza las tres pistas que faltaron en las plaquetas impresas</t>
         </is>
       </c>
       <c r="C25" s="70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="71" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="E25" s="72">
         <f>C25*D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="74" t="inlineStr">
+        <is>
+          <t>Un hilo del cable de red sobrante. Principal: J4-3 ↔ J5-5 (GPIO 34) y J8-1 ↔ J5-6 (GPIO 35). Nivel 2: U3 ↔ R7 (GPIO 19). Sin costo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1" s="59">
+      <c r="A26" s="85" t="n"/>
+      <c r="B26" s="86" t="inlineStr">
+        <is>
+          <t>Subtotal bloque</t>
+        </is>
+      </c>
+      <c r="C26" s="87" t="n"/>
+      <c r="D26" s="88" t="n"/>
+      <c r="E26" s="89">
+        <f>SUM(E6:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="90" t="n"/>
+      <c r="G26" s="91" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="59"/>
+    <row r="28" ht="18.75" customHeight="1" s="59">
+      <c r="A28" s="92" t="inlineStr">
+        <is>
+          <t>BLOQUE C, Sensor de pasada (INCLUIDO EN ESTA ETAPA)</t>
+        </is>
+      </c>
+      <c r="B28" s="93" t="n"/>
+      <c r="C28" s="93" t="n"/>
+      <c r="D28" s="93" t="n"/>
+      <c r="E28" s="93" t="n"/>
+      <c r="F28" s="93" t="n"/>
+      <c r="G28" s="94" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="59">
+      <c r="A29" s="95" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="B29" s="96" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="C29" s="96" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="D29" s="96" t="inlineStr">
+        <is>
+          <t>Precio unit.</t>
+        </is>
+      </c>
+      <c r="E29" s="96" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="F29" s="96" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="G29" s="97" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="53.25" customHeight="1" s="59">
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>Sensor inductivo LJ12A3-4-Z/BX (NPN 6–36V)</t>
+        </is>
+      </c>
+      <c r="B30" s="125" t="inlineStr">
+        <is>
+          <t>Sensor de pasada recomendado, inmune a la pelusa. Es lo que le da al ESP32 el "entendimiento" de movimiento y posición del telar</t>
+        </is>
+      </c>
+      <c r="C30" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="71" t="n">
         <v>7000</v>
-      </c>
-      <c r="F25" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G25" s="74" t="inlineStr">
-        <is>
-          <t>Ya se tiene. Montado el 10/09/2026 sobre un eje que da una vuelta por pasada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="47" customHeight="1" s="59">
-      <c r="A26" s="68" t="inlineStr">
-        <is>
-          <t>(no aplica) Regulador 7824</t>
-        </is>
-      </c>
-      <c r="B26" s="129" t="inlineStr">
-        <is>
-          <t>Ya no es necesario: el telar entrega 12 a 14 V continuos, muy por debajo de los 36 V que tolera el sensor</t>
-        </is>
-      </c>
-      <c r="C26" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="71" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E26" s="72">
-        <f>C26*D26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G26" s="128" t="inlineStr">
-        <is>
-          <t>No se usa: el telar da 12 a 14 V continuos, dentro del rango del sensor (6 a 36 V).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32.5" customHeight="1" s="59">
-      <c r="A27" s="68" t="inlineStr">
-        <is>
-          <t>Optoacoplador PC817</t>
-        </is>
-      </c>
-      <c r="B27" s="129" t="inlineStr">
-        <is>
-          <t>Aísla la señal del sensor inductivo (hasta 36V) del GPIO del ESP32</t>
-        </is>
-      </c>
-      <c r="C27" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="71" t="n">
-        <v>700</v>
-      </c>
-      <c r="E27" s="72">
-        <f>C27*D27</f>
-        <v>1400</v>
-      </c>
-      <c r="F27" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G27" s="130" t="inlineStr">
-        <is>
-          <t>Uno en uso y uno de repuesto. Mismo componente que el sensado del Bloque A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32.5" customHeight="1" s="59">
-      <c r="A28" s="68" t="inlineStr">
-        <is>
-          <t>(no aplica) Puente rectificador DB157</t>
-        </is>
-      </c>
-      <c r="B28" s="125" t="inlineStr">
-        <is>
-          <t>Ya no es necesario para este bloque: la alimentación del sensor ya viene en continua</t>
-        </is>
-      </c>
-      <c r="C28" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="71" t="n">
-        <v>500</v>
-      </c>
-      <c r="E28" s="72">
-        <f>C28*D28</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G28" s="74" t="inlineStr">
-        <is>
-          <t>Ya se tiene</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="61.75" customHeight="1" s="59">
-      <c r="A29" s="68" t="inlineStr">
-        <is>
-          <t>Cable 3 conectores (para sensor inductivo)</t>
-        </is>
-      </c>
-      <c r="B29" s="80" t="inlineStr">
-        <is>
-          <t>Conexión entre el gabinete y el sensor inductivo</t>
-        </is>
-      </c>
-      <c r="C29" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="71" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E29" s="72">
-        <f>C29*D29</f>
-        <v>5100</v>
-      </c>
-      <c r="F29" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G29" s="74" t="inlineStr">
-        <is>
-          <t>Ya se tiene. Al gabinete llegan dos hilos: el positivo del telar (el mismo punto del marrón) y el negro del sensor; el azul queda en el negativo del telar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32.5" customHeight="1" s="59">
-      <c r="A30" s="68" t="inlineStr">
-        <is>
-          <t>Resistencia 1,2 kΩ ¼ W</t>
-        </is>
-      </c>
-      <c r="B30" s="69" t="inlineStr">
-        <is>
-          <t>Limita la corriente del LED del optoacoplador. Con 13 V da unos 10 mA, el valor de trabajo del PC817</t>
-        </is>
-      </c>
-      <c r="C30" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="71" t="n">
-        <v>150</v>
       </c>
       <c r="E30" s="72">
         <f>C30*D30</f>
-        <v>300</v>
+        <v/>
       </c>
       <c r="F30" s="98" t="inlineStr">
         <is>
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G30" s="100" t="inlineStr">
-        <is>
-          <t>Uno en uso y uno de repuesto.</t>
+      <c r="G30" s="74" t="inlineStr">
+        <is>
+          <t>Ya se tiene. Montado el 10/09/2026 sobre un eje que da una vuelta por pasada.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32.5" customHeight="1" s="59">
       <c r="A31" s="68" t="inlineStr">
         <is>
-          <t>Resistencia 10kΩ ¼W</t>
-        </is>
-      </c>
-      <c r="B31" s="69" t="inlineStr">
-        <is>
-          <t>Pull-up del GPIO del sensor</t>
+          <t>Optoacoplador PC817</t>
+        </is>
+      </c>
+      <c r="B31" s="129" t="inlineStr">
+        <is>
+          <t>Aísla la señal del sensor inductivo (hasta 36V) del GPIO del ESP32</t>
         </is>
       </c>
       <c r="C31" s="70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="71" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="E31" s="72">
         <f>C31*D31</f>
-        <v>150</v>
+        <v/>
       </c>
       <c r="F31" s="98" t="inlineStr">
         <is>
@@ -1959,257 +1959,257 @@
       </c>
       <c r="G31" s="130" t="inlineStr">
         <is>
-          <t>Mantiene el pin del ESP32 en nivel alto mientras el sensor no detecta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32.5" customHeight="1" s="59">
+          <t>Uno en uso y uno de repuesto. Mismo componente que el sensado del Bloque A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="61.75" customHeight="1" s="59">
       <c r="A32" s="68" t="inlineStr">
         <is>
-          <t>(no aplica) Capacitor cerámico 100 nF</t>
-        </is>
-      </c>
-      <c r="B32" s="69" t="inlineStr">
-        <is>
-          <t>Acompañaba al regulador, que ya no se usa</t>
+          <t>Cable 3 conectores (para sensor inductivo)</t>
+        </is>
+      </c>
+      <c r="B32" s="80" t="inlineStr">
+        <is>
+          <t>Conexión entre el gabinete y el sensor inductivo</t>
         </is>
       </c>
       <c r="C32" s="70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D32" s="71" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="E32" s="72">
         <f>C32*D32</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F32" s="98" t="inlineStr">
         <is>
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G32" s="130" t="inlineStr">
-        <is>
-          <t>No se usa: acompañaba al regulador 7824, que se descartó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="61.75" customHeight="1" s="59">
+      <c r="G32" s="74" t="inlineStr">
+        <is>
+          <t>Ya se tiene. Al gabinete llegan dos hilos: el positivo del telar (el mismo punto del marrón) y el negro del sensor; el azul queda en el negativo del telar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32.5" customHeight="1" s="59">
       <c r="A33" s="68" t="inlineStr">
         <is>
-          <t>Blanco metálico y soporte</t>
-        </is>
-      </c>
-      <c r="B33" s="69" t="inlineStr">
-        <is>
-          <t>Paleta de acero sobre el eje y escuadra de montaje. Soporte ya construido</t>
+          <t>Resistencia 1,2 kΩ ¼ W</t>
+        </is>
+      </c>
+      <c r="B33" s="125" t="inlineStr">
+        <is>
+          <t>Limita la corriente del LED del optoacoplador. Con 13 V da unos 10 mA, el valor de trabajo del PC817</t>
         </is>
       </c>
       <c r="C33" s="70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" s="71" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E33" s="72">
         <f>C33*D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="98" t="inlineStr">
+        <is>
+          <t>Comprado en el local</t>
+        </is>
+      </c>
+      <c r="G33" s="100" t="inlineStr">
+        <is>
+          <t>Uno en uso y uno de repuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32.5" customHeight="1" s="59">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>Resistencia 10kΩ ¼W</t>
+        </is>
+      </c>
+      <c r="B34" s="125" t="inlineStr">
+        <is>
+          <t>Pull-up del GPIO del sensor</t>
+        </is>
+      </c>
+      <c r="C34" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="71" t="n">
+        <v>150</v>
+      </c>
+      <c r="E34" s="72">
+        <f>C34*D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="98" t="inlineStr">
+        <is>
+          <t>Comprado en el local</t>
+        </is>
+      </c>
+      <c r="G34" s="130" t="inlineStr">
+        <is>
+          <t>Mantiene el pin del ESP32 en nivel alto mientras el sensor no detecta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="61.75" customHeight="1" s="59">
+      <c r="A35" s="68" t="inlineStr">
+        <is>
+          <t>Blanco metálico y soporte</t>
+        </is>
+      </c>
+      <c r="B35" s="125" t="inlineStr">
+        <is>
+          <t>Paleta de acero sobre el eje y escuadra de montaje. Soporte ya construido</t>
+        </is>
+      </c>
+      <c r="C35" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="98" t="inlineStr">
+      <c r="D35" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="72">
+        <f>C35*D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="98" t="inlineStr">
         <is>
           <t>Comprado en el local</t>
         </is>
       </c>
-      <c r="G33" s="101" t="inlineStr">
+      <c r="G35" s="130" t="inlineStr">
         <is>
           <t>Ya construido y montado el 10/09/2026: escuadra en L tomada de un tornillo existente del chasis, más un tornillo o chapa como blanco metálico.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20.25" customHeight="1" s="59">
-      <c r="A34" s="102" t="n"/>
-      <c r="B34" s="86" t="inlineStr">
+    <row r="36" ht="20.25" customHeight="1" s="59">
+      <c r="A36" s="102" t="n"/>
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>Subtotal bloque</t>
         </is>
       </c>
-      <c r="C34" s="87" t="n"/>
-      <c r="D34" s="88" t="n"/>
-      <c r="E34" s="103">
-        <f>SUM(E25:E33)</f>
-        <v>13950</v>
-      </c>
-      <c r="F34" s="104" t="n"/>
-      <c r="G34" s="90" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" s="59"/>
-    <row r="36" ht="20.25" customHeight="1" s="59">
-      <c r="A36" s="92" t="inlineStr">
+      <c r="C36" s="87" t="n"/>
+      <c r="D36" s="88" t="n"/>
+      <c r="E36" s="103">
+        <f>SUM(E30:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="104" t="n"/>
+      <c r="G36" s="90" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="59"/>
+    <row r="38" ht="20.25" customHeight="1" s="59">
+      <c r="A38" s="92" t="inlineStr">
         <is>
           <t>BLOQUE D, Nivel 2: BOBINAS DE SELECCIÓN (4 canales en el C 201)</t>
         </is>
       </c>
-      <c r="B36" s="93" t="n"/>
-      <c r="C36" s="93" t="n"/>
-      <c r="D36" s="93" t="n"/>
-      <c r="E36" s="93" t="n"/>
-      <c r="F36" s="93" t="n"/>
-      <c r="G36" s="94" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="59">
-      <c r="A37" s="105" t="inlineStr">
+      <c r="B38" s="93" t="n"/>
+      <c r="C38" s="93" t="n"/>
+      <c r="D38" s="93" t="n"/>
+      <c r="E38" s="93" t="n"/>
+      <c r="F38" s="93" t="n"/>
+      <c r="G38" s="94" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="59">
+      <c r="A39" s="105" t="inlineStr">
         <is>
           <t>Componente</t>
         </is>
       </c>
-      <c r="B37" s="106" t="inlineStr">
+      <c r="B39" s="106" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C37" s="106" t="inlineStr">
+      <c r="C39" s="106" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="D37" s="106" t="inlineStr">
+      <c r="D39" s="106" t="inlineStr">
         <is>
           <t>Precio unit.</t>
         </is>
       </c>
-      <c r="E37" s="106" t="inlineStr">
+      <c r="E39" s="106" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="F37" s="106" t="inlineStr">
+      <c r="F39" s="106" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="G37" s="107" t="inlineStr">
+      <c r="G39" s="107" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="76.25" customHeight="1" s="59">
-      <c r="A38" s="68" t="inlineStr">
+    <row r="40" ht="76.25" customHeight="1" s="59">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>Bobinas de selección del telar (YA INSTALADAS)</t>
         </is>
       </c>
-      <c r="B38" s="69" t="inlineStr">
+      <c r="B40" s="125" t="inlineStr">
         <is>
           <t>El actuador: empuja la palanca de selección. El C 201 tiene cuatro</t>
         </is>
       </c>
-      <c r="C38" s="70" t="n">
+      <c r="C40" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="71" t="n">
+      <c r="D40" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="72">
-        <f>C38*D38</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="98" t="inlineStr">
+      <c r="E40" s="72">
+        <f>C40*D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="108" t="inlineStr">
+      <c r="G40" s="108" t="inlineStr">
         <is>
           <t>El C 201 tiene 4 bobinas en funcionamiento, confirmado con el dueño el 19/09/26. No hay que comprarlas ni montarlas: el sistema solo interviene la señal del lector óptico que las comanda.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="252" customHeight="1" s="59">
-      <c r="A39" s="68" t="inlineStr">
+    <row r="41" ht="252" customHeight="1" s="59">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>Relé OptoMOS LCA110 de IXYS (DIP-6)</t>
         </is>
       </c>
-      <c r="B39" s="69" t="inlineStr">
+      <c r="B41" s="125" t="inlineStr">
         <is>
           <t>Da la señal en lugar de cada lector óptico (conexión final), comandado directo desde un pin del ESP32</t>
         </is>
       </c>
-      <c r="C39" s="70" t="n">
+      <c r="C41" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="71" t="n">
+      <c r="D41" s="71" t="n">
         <v>6034</v>
-      </c>
-      <c r="E39" s="72">
-        <f>C39*D39</f>
-        <v>24136</v>
-      </c>
-      <c r="F39" s="98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="101" t="inlineStr">
-        <is>
-          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1 (cada uno con su propia disposición de patas). Conexión final: el relé en lugar del lector, con una resistencia de protección (diagramas/hardware/conexion_final_rele.png). Comprar 1 y probarlo antes de los otros 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="47" customHeight="1" s="59">
-      <c r="A40" s="68" t="inlineStr">
-        <is>
-          <t>Borneras atornillables chicas</t>
-        </is>
-      </c>
-      <c r="B40" s="69" t="inlineStr">
-        <is>
-          <t>Empalme al cableado del telar sin soldar sobre los cables viejos</t>
-        </is>
-      </c>
-      <c r="C40" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" s="109" t="n">
-        <v>600</v>
-      </c>
-      <c r="E40" s="110">
-        <f>C40*D40</f>
-        <v>3600</v>
-      </c>
-      <c r="F40" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G40" s="130" t="inlineStr">
-        <is>
-          <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos. Las del conector de cada lector son las de 4 vías (abajo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="33.75" customHeight="1" s="59">
-      <c r="A41" s="68" t="inlineStr">
-        <is>
-          <t>Cable para los 4 canales</t>
-        </is>
-      </c>
-      <c r="B41" s="125" t="inlineStr">
-        <is>
-          <t>Conexión entre el gabinete y el conector de cada lector</t>
-        </is>
-      </c>
-      <c r="C41" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" s="71" t="n">
-        <v>700</v>
       </c>
       <c r="E41" s="72">
         <f>C41*D41</f>
-        <v>5600</v>
+        <v/>
       </c>
       <c r="F41" s="98" t="inlineStr">
         <is>
@@ -2218,152 +2218,158 @@
       </c>
       <c r="G41" s="130" t="inlineStr">
         <is>
+          <t>Uno por lector óptico: son 4, uno por bobina de selección, confirmado con el dueño el 19/09/26. Soporta 350 V y 120 mA, con salida MOSFET: funciona con continua o alterna y no tiene corriente mínima. Se elige en lugar de un SSR de triac porque el triac necesita 0,1 A para mantenerse encendido y la señal del lector maneja pocos miliamperes. IMPORTANTE: pedir la versión DIP de seis patas (inserción); la SOP-6 es de montaje superficial. Patas: 1 y 2 el LED de control, 4 y 6 la salida, 3 y 5 sin conectar. Alternativas con el mismo principio: AQY212GH, G3VM-61A1 (cada uno con su propia disposición de patas). Conexión final: el relé en lugar del lector, con una resistencia de protección (diagramas/hardware/conexion_final_rele.png). Comprar 1 y probarlo antes de los otros 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="47" customHeight="1" s="59">
+      <c r="A42" s="68" t="inlineStr">
+        <is>
+          <t>Borneras atornillables chicas</t>
+        </is>
+      </c>
+      <c r="B42" s="125" t="inlineStr">
+        <is>
+          <t>Empalme al cableado del telar sin soldar sobre los cables viejos</t>
+        </is>
+      </c>
+      <c r="C42" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="109" t="n">
+        <v>600</v>
+      </c>
+      <c r="E42" s="110">
+        <f>C42*D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="98" t="inlineStr">
+        <is>
+          <t>Comprado en el local</t>
+        </is>
+      </c>
+      <c r="G42" s="130" t="inlineStr">
+        <is>
+          <t>Para el conexionado de los cuatro canales dentro del gabinete, más repuestos. Las del conector de cada lector son las de 4 vías (abajo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="33.75" customHeight="1" s="59">
+      <c r="A43" s="68" t="inlineStr">
+        <is>
+          <t>Cable para los 4 canales</t>
+        </is>
+      </c>
+      <c r="B43" s="125" t="inlineStr">
+        <is>
+          <t>Conexión entre el gabinete y el conector de cada lector</t>
+        </is>
+      </c>
+      <c r="C43" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" s="71" t="n">
+        <v>700</v>
+      </c>
+      <c r="E43" s="72">
+        <f>C43*D43</f>
+        <v/>
+      </c>
+      <c r="F43" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="130" t="inlineStr">
+        <is>
           <t>Se aprovecha el sobrante del cable del Bloque A. Cantidad a definir según el recorrido real.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42.75" customHeight="1" s="59">
-      <c r="A42" s="68" t="inlineStr">
+    <row r="44" ht="42.75" customHeight="1" s="59">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>Resistencia 10kΩ ¼W</t>
         </is>
       </c>
-      <c r="B42" s="69" t="inlineStr">
+      <c r="B44" s="125" t="inlineStr">
         <is>
           <t>Polarización de las 4 salidas del ESP32 hacia los relés</t>
         </is>
       </c>
-      <c r="C42" s="70" t="n">
+      <c r="C44" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="71" t="n">
+      <c r="D44" s="71" t="n">
         <v>150</v>
       </c>
-      <c r="E42" s="72">
-        <f>C42*D42</f>
-        <v>600</v>
-      </c>
-      <c r="F42" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G42" s="74" t="inlineStr">
-        <is>
-          <t>Una por canal: polarizan las 4 salidas del ESP32 para el arranque seguro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="61.75" customHeight="1" s="59">
-      <c r="A43" s="68" t="inlineStr">
-        <is>
-          <t>Resistencia 330 Ω ¼ W</t>
-        </is>
-      </c>
-      <c r="B43" s="125" t="inlineStr">
-        <is>
-          <t>Limita la corriente del LED de entrada de cada relé LCA110</t>
-        </is>
-      </c>
-      <c r="C43" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="71" t="n">
-        <v>150</v>
-      </c>
-      <c r="E43" s="110">
-        <f>C43*D43</f>
-        <v>600</v>
-      </c>
-      <c r="F43" s="98" t="inlineStr">
-        <is>
-          <t>Comprado en el local</t>
-        </is>
-      </c>
-      <c r="G43" s="130" t="inlineStr">
-        <is>
-          <t>Una por canal. Con los 3,3 V del ESP32 entrega unos 6 mA. NO es opcional: sin ella se daña el LED del relé. El SSR de triac no la necesita porque la trae incorporada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="61.75" customHeight="1" s="59">
-      <c r="A44" s="68" t="inlineStr">
-        <is>
-          <t>Placa experimental (plaqueta) adicional</t>
-        </is>
-      </c>
-      <c r="B44" s="69" t="inlineStr">
-        <is>
-          <t>Pasar a placa soldada el circuito del Nivel 2 que ya funcionó en protoboard</t>
-        </is>
-      </c>
-      <c r="C44" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="71" t="n"/>
       <c r="E44" s="72">
         <f>C44*D44</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F44" s="98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Comprado en el local</t>
         </is>
       </c>
       <c r="G44" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 10/10/2026, con todo probado en protoboard. Ya está soldada (20/10/2026). Precio a completar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="33.75" customHeight="1" s="59">
+          <t>Una por canal: polarizan las 4 salidas del ESP32 para el arranque seguro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="61.75" customHeight="1" s="59">
       <c r="A45" s="68" t="inlineStr">
         <is>
-          <t>Tira de pines de 2 (2x)</t>
-        </is>
-      </c>
-      <c r="B45" s="69" t="inlineStr">
-        <is>
-          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+          <t>Resistencia 330 Ω ¼ W</t>
+        </is>
+      </c>
+      <c r="B45" s="125" t="inlineStr">
+        <is>
+          <t>Limita la corriente del LED de entrada de cada relé LCA110</t>
         </is>
       </c>
       <c r="C45" s="70" t="n">
-        <v>19</v>
-      </c>
-      <c r="D45" s="71" t="n"/>
-      <c r="E45" s="72">
+        <v>4</v>
+      </c>
+      <c r="D45" s="71" t="n">
+        <v>150</v>
+      </c>
+      <c r="E45" s="110">
         <f>C45*D45</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F45" s="98" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="74" t="inlineStr">
-        <is>
-          <t>Se suma el 10/10/2026. Permiten sacar módulos y cables sin desoldar. Precio a completar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="33.75" customHeight="1" s="59">
+          <t>Comprado en el local</t>
+        </is>
+      </c>
+      <c r="G45" s="130" t="inlineStr">
+        <is>
+          <t>Una por canal. Con los 3,3 V del ESP32 entrega unos 6 mA. NO es opcional: sin ella se daña el LED del relé. El SSR de triac no la necesita porque la trae incorporada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="61.75" customHeight="1" s="59">
       <c r="A46" s="68" t="inlineStr">
         <is>
-          <t>Tira de pines de 5 (5x)</t>
-        </is>
-      </c>
-      <c r="B46" s="69" t="inlineStr">
-        <is>
-          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
+          <t>Placa para la plaqueta del Nivel 2</t>
+        </is>
+      </c>
+      <c r="B46" s="125" t="inlineStr">
+        <is>
+          <t>La plaqueta impresa del Nivel 2 (sensor de pasada y los 4 relés LCA110), diseñada en Proteus</t>
         </is>
       </c>
       <c r="C46" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="D46" s="71" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="D46" s="71" t="n">
+        <v>3000</v>
+      </c>
       <c r="E46" s="72">
         <f>C46*D46</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F46" s="98" t="inlineStr">
         <is>
@@ -2372,28 +2378,30 @@
       </c>
       <c r="G46" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 10/10/2026. Precio a completar.</t>
+          <t>Se suma el 10/10/2026, con todo probado en protoboard. Ya está soldada (20/10/2026) e instalada en el gabinete (28/10/2026). Precio estimado (local, octubre de 2026).</t>
         </is>
       </c>
     </row>
     <row r="47" ht="33.75" customHeight="1" s="59">
       <c r="A47" s="68" t="inlineStr">
         <is>
-          <t>Tira de pines de 6 (6x)</t>
-        </is>
-      </c>
-      <c r="B47" s="69" t="inlineStr">
+          <t>Tira de pines de 2 (2x)</t>
+        </is>
+      </c>
+      <c r="B47" s="125" t="inlineStr">
         <is>
           <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
         </is>
       </c>
       <c r="C47" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" s="71" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="D47" s="71" t="n">
+        <v>100</v>
+      </c>
       <c r="E47" s="72">
         <f>C47*D47</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F47" s="98" t="inlineStr">
         <is>
@@ -2402,28 +2410,30 @@
       </c>
       <c r="G47" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 10/10/2026. Precio a completar.</t>
+          <t>Se suma el 10/10/2026. Permiten sacar módulos y cables sin desoldar. Precio estimado (local, octubre de 2026).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="33.75" customHeight="1" s="59">
       <c r="A48" s="68" t="inlineStr">
         <is>
-          <t>Tira de pines de 8 (8x)</t>
-        </is>
-      </c>
-      <c r="B48" s="69" t="inlineStr">
+          <t>Tira de pines de 5 (5x)</t>
+        </is>
+      </c>
+      <c r="B48" s="125" t="inlineStr">
         <is>
           <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
         </is>
       </c>
       <c r="C48" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="71" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="D48" s="71" t="n">
+        <v>200</v>
+      </c>
       <c r="E48" s="72">
         <f>C48*D48</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F48" s="98" t="inlineStr">
         <is>
@@ -2432,28 +2442,30 @@
       </c>
       <c r="G48" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 10/10/2026. Precio a completar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="45" customHeight="1" s="59">
+          <t>Se suma el 10/10/2026. Precio estimado (local, octubre de 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="33.75" customHeight="1" s="59">
       <c r="A49" s="68" t="inlineStr">
         <is>
-          <t>Zócalo DIP de 6 patas</t>
-        </is>
-      </c>
-      <c r="B49" s="69" t="inlineStr">
-        <is>
-          <t>Permite cambiar un relé LCA110 sin desoldar</t>
+          <t>Tira de pines de 6 (6x)</t>
+        </is>
+      </c>
+      <c r="B49" s="125" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
         </is>
       </c>
       <c r="C49" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="D49" s="71" t="n"/>
+      <c r="D49" s="71" t="n">
+        <v>250</v>
+      </c>
       <c r="E49" s="72">
         <f>C49*D49</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F49" s="98" t="inlineStr">
         <is>
@@ -2462,28 +2474,30 @@
       </c>
       <c r="G49" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 11/10/2026: el relé va enchufado en el zócalo, con la muesca del lado de la pata 1. Precio a completar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="91" customHeight="1" s="59">
+          <t>Se suma el 10/10/2026. Precio estimado (local, octubre de 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="33.75" customHeight="1" s="59">
       <c r="A50" s="68" t="inlineStr">
         <is>
-          <t>Resistencia de protección 470 Ω 3 W</t>
-        </is>
-      </c>
-      <c r="B50" s="69" t="inlineStr">
-        <is>
-          <t>Lado del telar: limita la corriente si hay un error de cableado. Va del + del conector del lector a la pata 4 del relé</t>
+          <t>Tira de pines de 8 (8x)</t>
+        </is>
+      </c>
+      <c r="B50" s="125" t="inlineStr">
+        <is>
+          <t>Conectores enchufables para los cables y módulos de la plaqueta</t>
         </is>
       </c>
       <c r="C50" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="71" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="D50" s="71" t="n">
+        <v>300</v>
+      </c>
       <c r="E50" s="72">
         <f>C50*D50</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F50" s="98" t="inlineStr">
         <is>
@@ -2492,28 +2506,30 @@
       </c>
       <c r="G50" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 11/10/2026 con la conexión final (la más segura). 220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V: se elige con la medición. En el C 201 dio entre 15 y 30 V (17/10/2026): van las de 470 Ω 3 W. Precio a completar.</t>
+          <t>Se suma el 10/10/2026. Precio estimado (local, octubre de 2026).</t>
         </is>
       </c>
     </row>
     <row r="51" ht="45" customHeight="1" s="59">
       <c r="A51" s="68" t="inlineStr">
         <is>
-          <t>Resistencia 10 kΩ ½ W</t>
-        </is>
-      </c>
-      <c r="B51" s="69" t="inlineStr">
-        <is>
-          <t>Lado del telar: de la señal al − de cada conector de lector. Con el relé abierto deja la señal en 0 V, como con papel</t>
+          <t>Zócalo DIP de 6 patas</t>
+        </is>
+      </c>
+      <c r="B51" s="125" t="inlineStr">
+        <is>
+          <t>Permite cambiar un relé LCA110 sin desoldar</t>
         </is>
       </c>
       <c r="C51" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="D51" s="71" t="n"/>
+      <c r="D51" s="71" t="n">
+        <v>300</v>
+      </c>
       <c r="E51" s="72">
         <f>C51*D51</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F51" s="98" t="inlineStr">
         <is>
@@ -2522,28 +2538,30 @@
       </c>
       <c r="G51" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 11/10/2026 con la conexión final. Una por canal. Precio a completar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="76.25" customHeight="1" s="59">
+          <t>Se suma el 11/10/2026: el relé va enchufado en el zócalo, con la muesca del lado de la pata 1. Precio estimado (local, octubre de 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="91" customHeight="1" s="59">
       <c r="A52" s="68" t="inlineStr">
         <is>
-          <t>Borneras de 4 vías</t>
-        </is>
-      </c>
-      <c r="B52" s="69" t="inlineStr">
-        <is>
-          <t>Conector de cada lector en la plaqueta del telar, y para dejar aislados los cables del lector</t>
+          <t>Resistencia de protección 470 Ω 3 W</t>
+        </is>
+      </c>
+      <c r="B52" s="125" t="inlineStr">
+        <is>
+          <t>Lado del telar: limita la corriente si hay un error de cableado. Va del + del conector del lector a la pata 4 del relé</t>
         </is>
       </c>
       <c r="C52" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="71" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="D52" s="71" t="n">
+        <v>400</v>
+      </c>
       <c r="E52" s="72">
         <f>C52*D52</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F52" s="98" t="inlineStr">
         <is>
@@ -2552,75 +2570,126 @@
       </c>
       <c r="G52" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 11/10/2026 con la conexión final. Por canal: una para el conector del lector y otra para dejar aislados y rotulados sus 4 cables, que se vuelven a conectar en minutos. Precio a completar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" s="59">
-      <c r="A53" s="111" t="n"/>
-      <c r="B53" s="112" t="inlineStr">
+          <t>Se suma el 11/10/2026 con la conexión final (la más segura). 220 Ω 2 W si el lector se alimenta con hasta 15 V; 470 Ω 3 W de 15 a 30 V: se elige con la medición. En el C 201 dio entre 15 y 30 V (17/10/2026): van las de 470 Ω 3 W. Precio estimado (local, octubre de 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1" s="59">
+      <c r="A53" s="68" t="inlineStr">
+        <is>
+          <t>Resistencia 10 kΩ ½ W</t>
+        </is>
+      </c>
+      <c r="B53" s="125" t="inlineStr">
+        <is>
+          <t>Lado del telar: de la señal al − de cada conector de lector. Con el relé abierto deja la señal en 0 V, como con papel</t>
+        </is>
+      </c>
+      <c r="C53" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" s="71" t="n">
+        <v>200</v>
+      </c>
+      <c r="E53" s="72">
+        <f>C53*D53</f>
+        <v/>
+      </c>
+      <c r="F53" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final. Una por canal. Precio estimado (local, octubre de 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="76.25" customHeight="1" s="59">
+      <c r="A54" s="68" t="inlineStr">
+        <is>
+          <t>Borneras de 4 vías</t>
+        </is>
+      </c>
+      <c r="B54" s="125" t="inlineStr">
+        <is>
+          <t>Conector de cada lector en la plaqueta del telar, y para dejar aislados los cables del lector</t>
+        </is>
+      </c>
+      <c r="C54" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="71" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E54" s="72">
+        <f>C54*D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="74" t="inlineStr">
+        <is>
+          <t>Se suma el 11/10/2026 con la conexión final. Por canal: una para el conector del lector y otra para dejar aislados y rotulados sus 4 cables, que se vuelven a conectar en minutos. Precio estimado (local, octubre de 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="59">
+      <c r="A55" s="111" t="n"/>
+      <c r="B55" s="112" t="inlineStr">
         <is>
           <t>Subtotal bloque</t>
         </is>
       </c>
-      <c r="C53" s="87" t="n"/>
-      <c r="D53" s="88" t="n"/>
-      <c r="E53" s="113">
-        <f>SUM(E38:E52)</f>
-        <v>34536</v>
-      </c>
-      <c r="F53" s="114" t="n"/>
-      <c r="G53" s="115" t="n"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" s="59"/>
-    <row r="55" ht="24" customHeight="1" s="59">
-      <c r="A55" s="116" t="inlineStr">
+      <c r="C55" s="87" t="n"/>
+      <c r="D55" s="88" t="n"/>
+      <c r="E55" s="113">
+        <f>SUM(E40:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="114" t="n"/>
+      <c r="G55" s="115" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="59"/>
+    <row r="57" ht="24" customHeight="1" s="59">
+      <c r="A57" s="116" t="inlineStr">
         <is>
           <t>TOTAL DEL PROYECTO COMPLETO (A + C + D)</t>
         </is>
       </c>
-      <c r="B55" s="117" t="n"/>
-      <c r="C55" s="118" t="n"/>
-      <c r="D55" s="118" t="n"/>
-      <c r="E55" s="119">
-        <f>E21+E34+E53</f>
-        <v>122139</v>
-      </c>
-      <c r="F55" s="120" t="n"/>
-      <c r="G55" s="121" t="n"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" s="59"/>
-    <row r="57" ht="21.75" customHeight="1" s="59">
-      <c r="A57" s="122" t="inlineStr">
-        <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 20/10/2026: el Nivel 2 (sensor de pasada y relé LCA110) se probó en protoboard el 10/10/2026 y en el telar el 17/10/2026, con el sensor y el primer canal: funcionó, y al 20/10/2026 las plaquetas para la instalación definitiva ya están soldadas.</t>
-        </is>
-      </c>
+      <c r="B57" s="117" t="n"/>
+      <c r="C57" s="118" t="n"/>
+      <c r="D57" s="118" t="n"/>
+      <c r="E57" s="119">
+        <f>E26+E36+E55</f>
+        <v/>
+      </c>
+      <c r="F57" s="120" t="n"/>
+      <c r="G57" s="121" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="59"/>
-    <row r="59" ht="15" customHeight="1" s="59"/>
-    <row r="60" ht="15" customHeight="1" s="59"/>
-    <row r="61" ht="15" customHeight="1" s="59">
-      <c r="A61" s="58" t="n"/>
-      <c r="C61" s="58" t="n"/>
-      <c r="F61" s="58" t="n"/>
-    </row>
+    <row r="59" ht="21.75" customHeight="1" s="59">
+      <c r="A59" s="122" t="inlineStr">
+        <is>
+          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 28/10/2026: todo comprado e instalado. El gabinete, con las plaquetas soldadas y la plaqueta del ESP32 (sumada el 25/10/2026), se probó completo en el telar el 28/10/2026 (Niveles 1 y 2, los cuatro canales) y funcionó. Los precios marcados como estimados se confirman con los comprobantes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" s="59"/>
+    <row r="61" ht="15" customHeight="1" s="59"/>
     <row r="62" ht="15" customHeight="1" s="59"/>
-    <row r="63" ht="15" customHeight="1" s="59">
-      <c r="A63" s="58" t="n"/>
-      <c r="F63" s="58" t="n"/>
-    </row>
+    <row r="63" ht="15" customHeight="1" s="59"/>
     <row r="64" ht="15" customHeight="1" s="59"/>
-    <row r="65" ht="15.75" customHeight="1" s="59">
-      <c r="A65" s="58" t="n"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" s="59">
-      <c r="A66" s="58" t="n"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" s="59"/>
-    <row r="68" ht="15.75" customHeight="1" s="59"/>
-    <row r="69" ht="15.75" customHeight="1" s="59"/>
-    <row r="70" ht="15.75" customHeight="1" s="59"/>
+    <row r="65" ht="15" customHeight="1" s="59"/>
+    <row r="66" ht="15" customHeight="1" s="59"/>
+    <row r="67" ht="15" customHeight="1" s="59"/>
+    <row r="68" ht="15" customHeight="1" s="59"/>
+    <row r="69" ht="15" customHeight="1" s="59"/>
+    <row r="70" ht="15" customHeight="1" s="59"/>
     <row r="71" ht="15.75" customHeight="1" s="59"/>
     <row r="72" ht="15.75" customHeight="1" s="59"/>
     <row r="73" ht="15.75" customHeight="1" s="59"/>
@@ -3555,32 +3624,25 @@
     <row r="1002" ht="15.75" customHeight="1" s="59"/>
     <row r="1003" ht="15.75" customHeight="1" s="59"/>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="F63:G63"/>
+  <mergeCells count="13">
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A57:B60"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:G3"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A59:B62"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="H1:Z3"/>
     <mergeCell ref="H4:Z252"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" display="https://candy-ho.com/producto/nodemcu-esp32-wifi-bluetooth-4-2-iot-wroom-esp32s-arduino/" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" display="https://candy-ho.com/producto/modulo-relay-rele-de-2-canales-5v-10a-arduino-pic-avr-2/" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" display="https://candy-ho.com/producto/tiras-de-40-pines-hembra-paso-2-54mm-recta-1-fila-arduino/   -  https://candy-ho.com/producto/pcb-placa-experimental-doble-7x9-prototipos-electronica-fr4/" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId3"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
+++ b/documentacion_proyecto/Lista_de_componentes_Control_Trama.xlsx
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G46" s="74" t="inlineStr">
         <is>
-          <t>Se suma el 10/10/2026, con todo probado en protoboard. Ya está soldada (20/10/2026) e instalada en el gabinete (28/10/2026). Precio estimado (local, octubre de 2026).</t>
+          <t>Se suma el 10/10/2026, con todo probado en protoboard. Ya está soldada (20/10/2026) e instalada en el gabinete (30/10/2026). Precio estimado (local, octubre de 2026).</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
     <row r="59" ht="21.75" customHeight="1" s="59">
       <c r="A59" s="122" t="inlineStr">
         <is>
-          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 28/10/2026: todo comprado e instalado. El gabinete, con las plaquetas soldadas y la plaqueta del ESP32 (sumada el 25/10/2026), se probó completo en el telar el 28/10/2026 (Niveles 1 y 2, los cuatro canales) y funcionó. Los precios marcados como estimados se confirman con los comprobantes.</t>
+          <t>• ORDEN DE COMPRA: (1) Bloque A: comprado e instalado en el telar (19/09/2026). (2) Medición de la alimentación y la señal de un lector óptico: hecha el 17/10/2026, entre 15 y 30 V (la velocidad ya está confirmada: 300 pasadas por minuto). (3) Recién entonces el Bloque D, con la conexión final: el relé en lugar del lector, con una resistencia de protección que se elige con esa medición. Estado al 30/10/2026: todo comprado e instalado. El gabinete, con las plaquetas soldadas y la plaqueta del ESP32 (sumada el 25/10/2026), se probó completo en el telar el 30/10/2026 (Niveles 1 y 2, los cuatro canales) y funcionó. Los precios marcados como estimados se confirman con los comprobantes.</t>
         </is>
       </c>
     </row>
